--- a/Nutzerstudie/Assets/Results/Analysis_Output/Identifikation/00_Identifikation_Einzelantworten.xlsx
+++ b/Nutzerstudie/Assets/Results/Analysis_Output/Identifikation/00_Identifikation_Einzelantworten.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Einzelantworten" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einzelantworten'!$A$1:$V$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einzelantworten'!$A$1:$V$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V169"/>
+  <dimension ref="A1:V181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,7 @@
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="23" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
@@ -774,7 +774,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="2" t="n">
         <v>1</v>
@@ -5072,12 +5072,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5086,74 +5086,74 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.7845151e-08</v>
+        <v>98139.09</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>98008.52</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="2" t="n">
-        <v>31.738</v>
+        <v>49.409</v>
       </c>
       <c r="I62" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1.64071606e-08</v>
+        <v>130.5699999999924</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.02259859416251884</v>
+        <v>2.554745953729939</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
       </c>
       <c r="O62" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62" t="b">
         <v>0</v>
       </c>
       <c r="Q62" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S62" s="2" t="n">
-        <v>0.0017845151</v>
+        <v>98139.09</v>
       </c>
       <c r="T62" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>98008.52</v>
       </c>
       <c r="U62" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V62" s="2" t="n">
-        <v>0.00164071606</v>
+        <v>130.5699999999924</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5162,17 +5162,17 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>98158.59</v>
+        <v>98818.39999999999</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="2" t="n">
-        <v>25.678</v>
+        <v>131.408</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>7</v>
@@ -5186,10 +5186,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>150.0699999999924</v>
+        <v>4301</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2.936284945058243</v>
+        <v>84.15380521554034</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -5209,46 +5209,46 @@
         </is>
       </c>
       <c r="S63" s="2" t="n">
-        <v>98158.59</v>
+        <v>98818.39999999999</v>
       </c>
       <c r="T63" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="U63" s="2" t="n">
         <v>5110.87999999999</v>
       </c>
       <c r="V63" s="2" t="n">
-        <v>150.0699999999924</v>
+        <v>4301</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>6.018962e-05</v>
+        <v>2.583618e-06</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="2" t="n">
-        <v>146.178</v>
+        <v>53.779</v>
       </c>
       <c r="I64" s="2" t="n">
         <v>8</v>
@@ -5262,10 +5262,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1.241439e-05</v>
+        <v>2.5821800096e-06</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>17.09910497159589</v>
+        <v>3.556595776329476</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="2" t="n">
         <v>100000</v>
@@ -5285,198 +5285,198 @@
         </is>
       </c>
       <c r="S64" s="2" t="n">
-        <v>6.018962</v>
+        <v>0.2583618</v>
       </c>
       <c r="T64" s="2" t="n">
-        <v>7.260401</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U64" s="2" t="n">
         <v>7.26025720096</v>
       </c>
       <c r="V64" s="2" t="n">
-        <v>1.241439</v>
+        <v>0.25821800096</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>103107.33</v>
+        <v>4.310516e-09</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="2" t="n">
-        <v>65.767</v>
+        <v>38.968</v>
       </c>
       <c r="I65" s="2" t="n">
         <v>9</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K65" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L65" s="2" t="n">
-        <v>12.06999999999243</v>
+        <v>7.259969948399999e-05</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.2361628525810126</v>
+        <v>99.9960434933357</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
       </c>
       <c r="O65" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S65" s="2" t="n">
-        <v>103107.33</v>
+        <v>0.0004310516</v>
       </c>
       <c r="T65" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401</v>
       </c>
       <c r="U65" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V65" s="2" t="n">
-        <v>12.06999999999243</v>
+        <v>7.259969948399999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>3.1291847e-08</v>
+        <v>101037.11</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>98008.52</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="2" t="n">
-        <v>87.122</v>
+        <v>44.285</v>
       </c>
       <c r="I66" s="2" t="n">
         <v>10</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K66" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>2.98538566e-08</v>
+        <v>3028.589999999997</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.0411195578526509</v>
+        <v>59.25770121779424</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
       </c>
       <c r="O66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="b">
         <v>0</v>
       </c>
       <c r="Q66" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S66" s="2" t="n">
-        <v>0.0031291847</v>
+        <v>101037.11</v>
       </c>
       <c r="T66" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>98008.52</v>
       </c>
       <c r="U66" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V66" s="2" t="n">
-        <v>0.00298538566</v>
+        <v>3028.589999999997</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>98070.74000000001</v>
+        <v>98177.44</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="2" t="n">
-        <v>14.895</v>
+        <v>33.943</v>
       </c>
       <c r="I67" s="2" t="n">
         <v>11</v>
@@ -5490,10 +5490,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L67" s="2" t="n">
-        <v>62.22000000000116</v>
+        <v>4941.959999999992</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1.217402873869105</v>
+        <v>96.69489402999095</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -5513,46 +5513,46 @@
         </is>
       </c>
       <c r="S67" s="2" t="n">
-        <v>98070.74000000001</v>
+        <v>98177.44</v>
       </c>
       <c r="T67" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="U67" s="2" t="n">
         <v>5110.87999999999</v>
       </c>
       <c r="V67" s="2" t="n">
-        <v>62.22000000000116</v>
+        <v>4941.959999999992</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>6.925494e-05</v>
+        <v>1.7322199e-07</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="2" t="n">
-        <v>78.086</v>
+        <v>36.092</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>12</v>
@@ -5566,16 +5566,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L68" s="2" t="n">
-        <v>3.349070000000003e-06</v>
+        <v>1.717839996e-07</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>4.612880656014729</v>
+        <v>0.2366086969719</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
       </c>
       <c r="O68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68" t="b">
         <v>0</v>
@@ -5589,139 +5589,139 @@
         </is>
       </c>
       <c r="S68" s="2" t="n">
-        <v>6.925494</v>
+        <v>0.017322199</v>
       </c>
       <c r="T68" s="2" t="n">
-        <v>7.260401</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U68" s="2" t="n">
         <v>7.26025720096</v>
       </c>
       <c r="V68" s="2" t="n">
-        <v>0.3349070000000003</v>
+        <v>0.01717839996</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>103107.33</v>
+        <v>6.896072e-05</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="2" t="n">
-        <v>48.303</v>
+        <v>113.19</v>
       </c>
       <c r="I69" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K69" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>12.06999999999243</v>
+        <v>3.643289999999999e-06</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.2361628525810126</v>
+        <v>5.018128007253322</v>
       </c>
       <c r="N69" t="b">
         <v>0</v>
       </c>
       <c r="O69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69" t="b">
         <v>0</v>
       </c>
       <c r="Q69" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S69" s="2" t="n">
-        <v>103107.33</v>
+        <v>6.896072</v>
       </c>
       <c r="T69" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401</v>
       </c>
       <c r="U69" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V69" s="2" t="n">
-        <v>12.06999999999243</v>
+        <v>0.3643289999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>9.532255e-07</v>
+        <v>98092.16</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>98008.52</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="2" t="n">
-        <v>183.99</v>
+        <v>72.581</v>
       </c>
       <c r="I70" s="2" t="n">
         <v>14</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>9.517875096e-07</v>
+        <v>83.63999999999942</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1.31095563594379</v>
+        <v>1.636508781266623</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
@@ -5733,54 +5733,54 @@
         <v>0</v>
       </c>
       <c r="Q70" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S70" s="2" t="n">
-        <v>0.09532255000000001</v>
+        <v>98092.16</v>
       </c>
       <c r="T70" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>98008.52</v>
       </c>
       <c r="U70" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V70" s="2" t="n">
-        <v>0.09517875096</v>
+        <v>83.63999999999942</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>98010.63</v>
+        <v>99289.03</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="2" t="n">
-        <v>45.795</v>
+        <v>277.851</v>
       </c>
       <c r="I71" s="2" t="n">
         <v>15</v>
@@ -5794,16 +5794,16 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L71" s="2" t="n">
-        <v>2.110000000000582</v>
+        <v>3830.369999999995</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.04128447547194585</v>
+        <v>74.94541057508692</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
       </c>
       <c r="O71" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="b">
         <v>0</v>
@@ -5817,27 +5817,27 @@
         </is>
       </c>
       <c r="S71" s="2" t="n">
-        <v>98010.63</v>
+        <v>99289.03</v>
       </c>
       <c r="T71" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="U71" s="2" t="n">
         <v>5110.87999999999</v>
       </c>
       <c r="V71" s="2" t="n">
-        <v>2.110000000000582</v>
+        <v>3830.369999999995</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5846,17 +5846,17 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>6.896072e-05</v>
+        <v>6.821413e-09</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="2" t="n">
-        <v>49.55</v>
+        <v>40.334</v>
       </c>
       <c r="I72" s="2" t="n">
         <v>16</v>
@@ -5870,16 +5870,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3.643289999999999e-06</v>
+        <v>5.3834226e-09</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>5.018128007253322</v>
+        <v>0.007414919955298784</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
       </c>
       <c r="O72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72" t="b">
         <v>0</v>
@@ -5893,27 +5893,27 @@
         </is>
       </c>
       <c r="S72" s="2" t="n">
-        <v>6.896072</v>
+        <v>0.0006821412999999999</v>
       </c>
       <c r="T72" s="2" t="n">
-        <v>7.260401</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U72" s="2" t="n">
         <v>7.26025720096</v>
       </c>
       <c r="V72" s="2" t="n">
-        <v>0.3643289999999999</v>
+        <v>0.00053834226</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5922,113 +5922,113 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>103110.4</v>
+        <v>5.426503e-05</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="2" t="n">
-        <v>29.395</v>
+        <v>83.563</v>
       </c>
       <c r="I73" s="2" t="n">
         <v>17</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K73" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L73" s="2" t="n">
-        <v>9</v>
+        <v>1.833898e-05</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.176094919074602</v>
+        <v>25.25940816197958</v>
       </c>
       <c r="N73" t="b">
         <v>0</v>
       </c>
       <c r="O73" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" t="b">
         <v>0</v>
       </c>
       <c r="Q73" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S73" s="2" t="n">
-        <v>103110.4</v>
+        <v>5.426502999999999</v>
       </c>
       <c r="T73" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401</v>
       </c>
       <c r="U73" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V73" s="2" t="n">
-        <v>9</v>
+        <v>1.833898</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.7845151e-08</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="2" t="n">
-        <v>25.174</v>
+        <v>31.738</v>
       </c>
       <c r="I74" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1.64071606e-08</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0</v>
+        <v>0.02259859416251884</v>
       </c>
       <c r="N74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" t="b">
         <v>1</v>
@@ -6037,71 +6037,71 @@
         <v>0</v>
       </c>
       <c r="Q74" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S74" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.0017845151</v>
       </c>
       <c r="T74" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U74" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V74" s="2" t="n">
-        <v>0</v>
+        <v>0.00164071606</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4.282086e-05</v>
+        <v>98158.59</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="2" t="n">
-        <v>17.854</v>
+        <v>25.678</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K75" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L75" s="2" t="n">
-        <v>2.978315e-05</v>
+        <v>150.0699999999924</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>41.02216929182877</v>
+        <v>2.936284945058243</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
@@ -6113,71 +6113,71 @@
         <v>0</v>
       </c>
       <c r="Q75" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S75" s="2" t="n">
-        <v>4.282086</v>
+        <v>98158.59</v>
       </c>
       <c r="T75" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U75" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V75" s="2" t="n">
-        <v>2.978315</v>
+        <v>150.0699999999924</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>102816.8</v>
+        <v>6.018962e-05</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="2" t="n">
-        <v>8.250999999999999</v>
+        <v>146.178</v>
       </c>
       <c r="I76" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K76" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>4808.279999999999</v>
+        <v>1.241439e-05</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>94.07929749866966</v>
+        <v>17.09910497159589</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
@@ -6189,35 +6189,35 @@
         <v>0</v>
       </c>
       <c r="Q76" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S76" s="2" t="n">
-        <v>102816.8</v>
+        <v>6.018962</v>
       </c>
       <c r="T76" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U76" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V76" s="2" t="n">
-        <v>4808.279999999999</v>
+        <v>1.241439</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6226,110 +6226,110 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>2.831073e-05</v>
+        <v>103107.33</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="2" t="n">
-        <v>10.711</v>
+        <v>65.767</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>9</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K77" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>2.83092920096e-05</v>
+        <v>12.06999999999243</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>38.99213378536611</v>
+        <v>0.2361628525810126</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
       </c>
       <c r="O77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S77" s="2" t="n">
-        <v>2.831073</v>
+        <v>103107.33</v>
       </c>
       <c r="T77" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U77" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V77" s="2" t="n">
-        <v>2.83092920096</v>
+        <v>12.06999999999243</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>103110.4</v>
+        <v>3.1291847e-08</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="2" t="n">
-        <v>9.26</v>
+        <v>87.122</v>
       </c>
       <c r="I78" s="2" t="n">
         <v>10</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K78" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>9</v>
+        <v>2.98538566e-08</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>0.176094919074602</v>
+        <v>0.0411195578526509</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
@@ -6341,71 +6341,71 @@
         <v>0</v>
       </c>
       <c r="Q78" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S78" s="2" t="n">
-        <v>103110.4</v>
+        <v>0.0031291847</v>
       </c>
       <c r="T78" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U78" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V78" s="2" t="n">
-        <v>9</v>
+        <v>0.00298538566</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4.3881446e-05</v>
+        <v>98070.74000000001</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="2" t="n">
-        <v>31.649</v>
+        <v>14.895</v>
       </c>
       <c r="I79" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K79" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>2.8722564e-05</v>
+        <v>62.22000000000116</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>39.56135878519856</v>
+        <v>1.217402873869105</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
@@ -6417,71 +6417,71 @@
         <v>0</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S79" s="2" t="n">
-        <v>4.3881446</v>
+        <v>98070.74000000001</v>
       </c>
       <c r="T79" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U79" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V79" s="2" t="n">
-        <v>2.872256399999999</v>
+        <v>62.22000000000116</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>103110.4</v>
+        <v>6.925494e-05</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="2" t="n">
-        <v>9.292999999999999</v>
+        <v>78.086</v>
       </c>
       <c r="I80" s="2" t="n">
         <v>12</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K80" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L80" s="2" t="n">
-        <v>5101.87999999999</v>
+        <v>3.349070000000003e-06</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>99.8239050809254</v>
+        <v>4.612880656014729</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
@@ -6493,35 +6493,35 @@
         <v>0</v>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S80" s="2" t="n">
-        <v>103110.4</v>
+        <v>6.925494</v>
       </c>
       <c r="T80" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U80" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V80" s="2" t="n">
-        <v>5101.87999999999</v>
+        <v>0.3349070000000003</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6530,262 +6530,262 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.5849711e-06</v>
+        <v>103107.33</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="2" t="n">
-        <v>16.978</v>
+        <v>48.303</v>
       </c>
       <c r="I81" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K81" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>1.5835331096e-06</v>
+        <v>12.06999999999243</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2.181097812059075</v>
+        <v>0.2361628525810126</v>
       </c>
       <c r="N81" t="b">
         <v>0</v>
       </c>
       <c r="O81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P81" t="b">
         <v>0</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S81" s="2" t="n">
-        <v>0.15849711</v>
+        <v>103107.33</v>
       </c>
       <c r="T81" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U81" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V81" s="2" t="n">
-        <v>0.15835331096</v>
+        <v>12.06999999999243</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>103110.4</v>
+        <v>9.532255e-07</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
       </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" s="2" t="n">
-        <v>9.605</v>
+        <v>183.99</v>
       </c>
       <c r="I82" s="2" t="n">
         <v>14</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K82" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>9</v>
+        <v>9.517875096e-07</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0.176094919074602</v>
+        <v>1.31095563594379</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
       </c>
       <c r="O82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" t="b">
         <v>0</v>
       </c>
       <c r="Q82" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S82" s="2" t="n">
-        <v>103110.4</v>
+        <v>0.09532255000000001</v>
       </c>
       <c r="T82" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U82" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V82" s="2" t="n">
-        <v>9</v>
+        <v>0.09517875096</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>4.243185e-05</v>
+        <v>98010.63</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="2" t="n">
-        <v>12.446</v>
+        <v>45.795</v>
       </c>
       <c r="I83" s="2" t="n">
         <v>15</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>3.017216e-05</v>
+        <v>2.110000000000582</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>41.55797675598935</v>
+        <v>0.04128447547194585</v>
       </c>
       <c r="N83" t="b">
         <v>0</v>
       </c>
       <c r="O83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P83" t="b">
         <v>0</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S83" s="2" t="n">
-        <v>4.243185</v>
+        <v>98010.63</v>
       </c>
       <c r="T83" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U83" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V83" s="2" t="n">
-        <v>3.017216</v>
+        <v>2.110000000000582</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>98121.08</v>
+        <v>6.896072e-05</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" s="2" t="n">
-        <v>13.389</v>
+        <v>49.55</v>
       </c>
       <c r="I84" s="2" t="n">
         <v>16</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>112.5599999999977</v>
+        <v>3.643289999999999e-06</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2.202360454559643</v>
+        <v>5.018128007253322</v>
       </c>
       <c r="N84" t="b">
         <v>0</v>
@@ -6797,35 +6797,35 @@
         <v>0</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S84" s="2" t="n">
-        <v>98121.08</v>
+        <v>6.896072</v>
       </c>
       <c r="T84" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U84" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V84" s="2" t="n">
-        <v>112.5599999999977</v>
+        <v>0.3643289999999999</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6834,34 +6834,34 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>3.9781443e-07</v>
+        <v>103110.4</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" s="2" t="n">
-        <v>11.048</v>
+        <v>29.395</v>
       </c>
       <c r="I85" s="2" t="n">
         <v>17</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>3.963764396e-07</v>
+        <v>9</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>0.5459537157273002</v>
+        <v>0.176094919074602</v>
       </c>
       <c r="N85" t="b">
         <v>0</v>
@@ -6873,111 +6873,111 @@
         <v>0</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S85" s="2" t="n">
-        <v>0.039781443</v>
+        <v>103110.4</v>
       </c>
       <c r="T85" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U85" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V85" s="2" t="n">
-        <v>0.03963764396</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.2736274e-06</v>
+        <v>103119.4</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" s="2" t="n">
-        <v>170.5</v>
+        <v>25.174</v>
       </c>
       <c r="I86" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1.2721894096e-06</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1.75226493275167</v>
+        <v>0</v>
       </c>
       <c r="N86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="b">
         <v>0</v>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S86" s="2" t="n">
-        <v>0.12736274</v>
+        <v>103119.4</v>
       </c>
       <c r="T86" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U86" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V86" s="2" t="n">
-        <v>0.12721894096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6986,34 +6986,34 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>101044.08</v>
+        <v>4.282086e-05</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" s="2" t="n">
-        <v>88.18300000000001</v>
+        <v>17.854</v>
       </c>
       <c r="I87" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>3035.559999999998</v>
+        <v>2.978315e-05</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>59.39407694956648</v>
+        <v>41.02216929182877</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
@@ -7025,35 +7025,35 @@
         <v>0</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S87" s="2" t="n">
-        <v>101044.08</v>
+        <v>4.282086</v>
       </c>
       <c r="T87" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U87" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V87" s="2" t="n">
-        <v>3035.559999999998</v>
+        <v>2.978315</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>4.490388e-05</v>
+        <v>102816.8</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" s="2" t="n">
-        <v>40.154</v>
+        <v>8.250999999999999</v>
       </c>
       <c r="I88" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K88" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2.770013e-05</v>
+        <v>4808.279999999999</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>38.15309738109182</v>
+        <v>94.07929749866966</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
@@ -7101,71 +7101,71 @@
         <v>0</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S88" s="2" t="n">
-        <v>4.490388</v>
+        <v>102816.8</v>
       </c>
       <c r="T88" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U88" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V88" s="2" t="n">
-        <v>2.770013</v>
+        <v>4808.279999999999</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>100879.53</v>
+        <v>2.831073e-05</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F89" t="b">
         <v>1</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" s="2" t="n">
-        <v>25.319</v>
+        <v>10.711</v>
       </c>
       <c r="I89" s="2" t="n">
         <v>9</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>2239.869999999995</v>
+        <v>2.83092920096e-05</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>43.82552515418088</v>
+        <v>38.99213378536611</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
@@ -7174,114 +7174,114 @@
         <v>0</v>
       </c>
       <c r="P89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q89" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S89" s="2" t="n">
-        <v>100879.53</v>
+        <v>2.831073</v>
       </c>
       <c r="T89" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U89" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V89" s="2" t="n">
-        <v>2239.869999999995</v>
+        <v>2.83092920096</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.5786655e-06</v>
+        <v>103110.4</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F90" t="b">
         <v>1</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" s="2" t="n">
-        <v>15.869</v>
+        <v>9.26</v>
       </c>
       <c r="I90" s="2" t="n">
         <v>10</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2.5772275096e-06</v>
+        <v>9</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3.549774392647167</v>
+        <v>0.176094919074602</v>
       </c>
       <c r="N90" t="b">
         <v>0</v>
       </c>
       <c r="O90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P90" t="b">
         <v>0</v>
       </c>
       <c r="Q90" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S90" s="2" t="n">
-        <v>0.25786655</v>
+        <v>103110.4</v>
       </c>
       <c r="T90" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U90" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V90" s="2" t="n">
-        <v>0.25772275096</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7290,34 +7290,34 @@
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>102271.46</v>
+        <v>4.3881446e-05</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F91" t="b">
         <v>1</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" s="2" t="n">
-        <v>29.765</v>
+        <v>31.649</v>
       </c>
       <c r="I91" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K91" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>4262.940000000002</v>
+        <v>2.8722564e-05</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>83.40911936887602</v>
+        <v>39.56135878519856</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
@@ -7329,35 +7329,35 @@
         <v>0</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S91" s="2" t="n">
-        <v>102271.46</v>
+        <v>4.3881446</v>
       </c>
       <c r="T91" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U91" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V91" s="2" t="n">
-        <v>4262.940000000002</v>
+        <v>2.872256399999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7366,34 +7366,34 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>4.000941e-05</v>
+        <v>103110.4</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" s="2" t="n">
-        <v>33.257</v>
+        <v>9.292999999999999</v>
       </c>
       <c r="I92" s="2" t="n">
         <v>12</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K92" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>3.25946e-05</v>
+        <v>5101.87999999999</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>44.89455276555509</v>
+        <v>99.8239050809254</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
@@ -7405,71 +7405,71 @@
         <v>0</v>
       </c>
       <c r="Q92" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S92" s="2" t="n">
-        <v>4.000941</v>
+        <v>103110.4</v>
       </c>
       <c r="T92" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U92" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V92" s="2" t="n">
-        <v>3.25946</v>
+        <v>5101.87999999999</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>100952.58</v>
+        <v>1.5849711e-06</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" s="2" t="n">
-        <v>19.707</v>
+        <v>16.978</v>
       </c>
       <c r="I93" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>2166.819999999992</v>
+        <v>1.5835331096e-06</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>42.39622139435863</v>
+        <v>2.181097812059075</v>
       </c>
       <c r="N93" t="b">
         <v>0</v>
@@ -7481,71 +7481,71 @@
         <v>0</v>
       </c>
       <c r="Q93" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S93" s="2" t="n">
-        <v>100952.58</v>
+        <v>0.15849711</v>
       </c>
       <c r="T93" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U93" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V93" s="2" t="n">
-        <v>2166.819999999992</v>
+        <v>0.15835331096</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>4.0766284e-07</v>
+        <v>103110.4</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F94" t="b">
         <v>1</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" s="2" t="n">
-        <v>19.504</v>
+        <v>9.605</v>
       </c>
       <c r="I94" s="2" t="n">
         <v>14</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K94" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>4.062248496e-07</v>
+        <v>9</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>0.5595185381948814</v>
+        <v>0.176094919074602</v>
       </c>
       <c r="N94" t="b">
         <v>0</v>
@@ -7557,35 +7557,35 @@
         <v>0</v>
       </c>
       <c r="Q94" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S94" s="2" t="n">
-        <v>0.040766284</v>
+        <v>103110.4</v>
       </c>
       <c r="T94" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U94" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V94" s="2" t="n">
-        <v>0.04062248496</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7594,34 +7594,34 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>98173.67</v>
+        <v>4.243185e-05</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F95" t="b">
         <v>1</v>
       </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" s="2" t="n">
-        <v>25.127</v>
+        <v>12.446</v>
       </c>
       <c r="I95" s="2" t="n">
         <v>15</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K95" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>165.1499999999942</v>
+        <v>3.017216e-05</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3.231341765018832</v>
+        <v>41.55797675598935</v>
       </c>
       <c r="N95" t="b">
         <v>0</v>
@@ -7633,35 +7633,35 @@
         <v>0</v>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S95" s="2" t="n">
-        <v>98173.67</v>
+        <v>4.243185</v>
       </c>
       <c r="T95" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U95" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V95" s="2" t="n">
-        <v>165.1499999999942</v>
+        <v>3.017216</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7670,34 +7670,34 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>4.921639e-05</v>
+        <v>98121.08</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" s="2" t="n">
-        <v>20.868</v>
+        <v>13.389</v>
       </c>
       <c r="I96" s="2" t="n">
         <v>16</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K96" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L96" s="2" t="n">
-        <v>2.338762e-05</v>
+        <v>112.5599999999977</v>
       </c>
       <c r="M96" s="2" t="n">
-        <v>32.21321139546893</v>
+        <v>2.202360454559643</v>
       </c>
       <c r="N96" t="b">
         <v>0</v>
@@ -7709,299 +7709,299 @@
         <v>0</v>
       </c>
       <c r="Q96" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S96" s="2" t="n">
-        <v>4.921639</v>
+        <v>98121.08</v>
       </c>
       <c r="T96" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U96" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V96" s="2" t="n">
-        <v>2.338762</v>
+        <v>112.5599999999977</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>100915.96</v>
+        <v>3.9781443e-07</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
       </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" s="2" t="n">
-        <v>14.743</v>
+        <v>11.048</v>
       </c>
       <c r="I97" s="2" t="n">
         <v>17</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L97" s="2" t="n">
-        <v>2203.439999999988</v>
+        <v>3.963764396e-07</v>
       </c>
       <c r="M97" s="2" t="n">
-        <v>43.11273205397098</v>
+        <v>0.5459537157273002</v>
       </c>
       <c r="N97" t="b">
         <v>0</v>
       </c>
       <c r="O97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P97" t="b">
         <v>0</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S97" s="2" t="n">
-        <v>100915.96</v>
+        <v>0.039781443</v>
       </c>
       <c r="T97" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U97" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V97" s="2" t="n">
-        <v>2203.439999999988</v>
+        <v>0.03963764396</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.2736274e-06</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
       </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" s="2" t="n">
-        <v>54.448</v>
+        <v>170.5</v>
       </c>
       <c r="I98" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1.2721894096e-06</v>
       </c>
       <c r="M98" s="2" t="n">
-        <v>0</v>
+        <v>1.75226493275167</v>
       </c>
       <c r="N98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P98" t="b">
         <v>0</v>
       </c>
       <c r="Q98" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S98" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.12736274</v>
       </c>
       <c r="T98" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U98" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V98" s="2" t="n">
-        <v>0</v>
+        <v>0.12721894096</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>101044.08</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F99" t="b">
         <v>1</v>
       </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" s="2" t="n">
-        <v>134.484</v>
+        <v>88.18300000000001</v>
       </c>
       <c r="I99" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K99" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L99" s="2" t="n">
-        <v>0</v>
+        <v>3035.559999999998</v>
       </c>
       <c r="M99" s="2" t="n">
-        <v>0</v>
+        <v>59.39407694956648</v>
       </c>
       <c r="N99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P99" t="b">
         <v>0</v>
       </c>
       <c r="Q99" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S99" s="2" t="n">
-        <v>7.260401</v>
+        <v>101044.08</v>
       </c>
       <c r="T99" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U99" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V99" s="2" t="n">
-        <v>0</v>
+        <v>3035.559999999998</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>98094.44</v>
+        <v>4.490388e-05</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" s="2" t="n">
-        <v>55.436</v>
+        <v>40.154</v>
       </c>
       <c r="I100" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K100" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>85.91999999999825</v>
+        <v>2.770013e-05</v>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1.681119494098833</v>
+        <v>38.15309738109182</v>
       </c>
       <c r="N100" t="b">
         <v>0</v>
@@ -8013,35 +8013,35 @@
         <v>0</v>
       </c>
       <c r="Q100" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S100" s="2" t="n">
-        <v>98094.44</v>
+        <v>4.490388</v>
       </c>
       <c r="T100" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U100" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V100" s="2" t="n">
-        <v>85.91999999999825</v>
+        <v>2.770013</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8050,186 +8050,186 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.7202063e-09</v>
+        <v>100879.53</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F101" t="b">
         <v>1</v>
       </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" s="2" t="n">
-        <v>126.562</v>
+        <v>25.319</v>
       </c>
       <c r="I101" s="2" t="n">
         <v>9</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K101" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>2.822159e-10</v>
+        <v>2239.869999999995</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>0.0003887133639875507</v>
+        <v>43.82552515418088</v>
       </c>
       <c r="N101" t="b">
         <v>0</v>
       </c>
       <c r="O101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P101" t="b">
         <v>0</v>
       </c>
       <c r="Q101" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S101" s="2" t="n">
-        <v>0.00017202063</v>
+        <v>100879.53</v>
       </c>
       <c r="T101" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U101" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V101" s="2" t="n">
-        <v>2.822159e-05</v>
+        <v>2239.869999999995</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>103110.4</v>
+        <v>2.5786655e-06</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F102" t="b">
         <v>1</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" s="2" t="n">
-        <v>82.965</v>
+        <v>15.869</v>
       </c>
       <c r="I102" s="2" t="n">
         <v>10</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K102" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>9</v>
+        <v>2.5772275096e-06</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>0.176094919074602</v>
+        <v>3.549774392647167</v>
       </c>
       <c r="N102" t="b">
         <v>0</v>
       </c>
       <c r="O102" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P102" t="b">
         <v>0</v>
       </c>
       <c r="Q102" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S102" s="2" t="n">
-        <v>103110.4</v>
+        <v>0.25786655</v>
       </c>
       <c r="T102" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U102" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V102" s="2" t="n">
-        <v>9</v>
+        <v>0.25772275096</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>5.2289022e-05</v>
+        <v>102271.46</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" s="2" t="n">
-        <v>40.705</v>
+        <v>29.765</v>
       </c>
       <c r="I103" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K103" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>2.0314988e-05</v>
+        <v>4262.940000000002</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>27.98108584543508</v>
+        <v>83.40911936887602</v>
       </c>
       <c r="N103" t="b">
         <v>0</v>
@@ -8241,111 +8241,111 @@
         <v>0</v>
       </c>
       <c r="Q103" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S103" s="2" t="n">
-        <v>5.2289022</v>
+        <v>102271.46</v>
       </c>
       <c r="T103" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U103" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V103" s="2" t="n">
-        <v>2.0314988</v>
+        <v>4262.940000000002</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>98017.36</v>
+        <v>4.000941e-05</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" s="2" t="n">
-        <v>35.471</v>
+        <v>33.257</v>
       </c>
       <c r="I104" s="2" t="n">
         <v>12</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K104" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>8.839999999996508</v>
+        <v>3.25946e-05</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>0.1729643427354296</v>
+        <v>44.89455276555509</v>
       </c>
       <c r="N104" t="b">
         <v>0</v>
       </c>
       <c r="O104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P104" t="b">
         <v>0</v>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S104" s="2" t="n">
-        <v>98017.36</v>
+        <v>4.000941</v>
       </c>
       <c r="T104" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U104" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V104" s="2" t="n">
-        <v>8.839999999996508</v>
+        <v>3.25946</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8354,34 +8354,34 @@
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1.2909707e-06</v>
+        <v>100952.58</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F105" t="b">
         <v>1</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" s="2" t="n">
-        <v>113.015</v>
+        <v>19.707</v>
       </c>
       <c r="I105" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K105" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>1.2895327096e-06</v>
+        <v>2166.819999999992</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1.776152929443725</v>
+        <v>42.39622139435863</v>
       </c>
       <c r="N105" t="b">
         <v>0</v>
@@ -8393,74 +8393,74 @@
         <v>0</v>
       </c>
       <c r="Q105" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S105" s="2" t="n">
-        <v>0.12909707</v>
+        <v>100952.58</v>
       </c>
       <c r="T105" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U105" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V105" s="2" t="n">
-        <v>0.12895327096</v>
+        <v>2166.819999999992</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>103119.4</v>
+        <v>4.0766284e-07</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
       </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" s="2" t="n">
-        <v>39.092</v>
+        <v>19.504</v>
       </c>
       <c r="I106" s="2" t="n">
         <v>14</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K106" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>0</v>
+        <v>4.062248496e-07</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>0</v>
+        <v>0.5595185381948814</v>
       </c>
       <c r="N106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="b">
         <v>1</v>
@@ -8469,71 +8469,71 @@
         <v>0</v>
       </c>
       <c r="Q106" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S106" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.040766284</v>
       </c>
       <c r="T106" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U106" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V106" s="2" t="n">
-        <v>0</v>
+        <v>0.04062248496</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>5.835816e-05</v>
+        <v>98173.67</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
       </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" s="2" t="n">
-        <v>256.433</v>
+        <v>25.127</v>
       </c>
       <c r="I107" s="2" t="n">
         <v>15</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K107" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>1.424585e-05</v>
+        <v>165.1499999999942</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>19.62168778003666</v>
+        <v>3.231341765018832</v>
       </c>
       <c r="N107" t="b">
         <v>0</v>
@@ -8545,71 +8545,71 @@
         <v>0</v>
       </c>
       <c r="Q107" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S107" s="2" t="n">
-        <v>5.835815999999999</v>
+        <v>98173.67</v>
       </c>
       <c r="T107" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U107" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V107" s="2" t="n">
-        <v>1.424585</v>
+        <v>165.1499999999942</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>98097.89999999999</v>
+        <v>4.921639e-05</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F108" t="b">
         <v>1</v>
       </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" s="2" t="n">
-        <v>49.395</v>
+        <v>20.868</v>
       </c>
       <c r="I108" s="2" t="n">
         <v>16</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K108" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>89.3799999999901</v>
+        <v>2.338762e-05</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1.748818207431798</v>
+        <v>32.21321139546893</v>
       </c>
       <c r="N108" t="b">
         <v>0</v>
@@ -8621,35 +8621,35 @@
         <v>0</v>
       </c>
       <c r="Q108" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S108" s="2" t="n">
-        <v>98097.89999999999</v>
+        <v>4.921639</v>
       </c>
       <c r="T108" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U108" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V108" s="2" t="n">
-        <v>89.3799999999901</v>
+        <v>2.338762</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8658,69 +8658,69 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.7202063e-09</v>
+        <v>100915.96</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F109" t="b">
         <v>1</v>
       </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" s="2" t="n">
-        <v>70.26000000000001</v>
+        <v>14.743</v>
       </c>
       <c r="I109" s="2" t="n">
         <v>17</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K109" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>2.822159e-10</v>
+        <v>2203.439999999988</v>
       </c>
       <c r="M109" s="2" t="n">
-        <v>0.0003887133639875507</v>
+        <v>43.11273205397098</v>
       </c>
       <c r="N109" t="b">
         <v>0</v>
       </c>
       <c r="O109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P109" t="b">
         <v>0</v>
       </c>
       <c r="Q109" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S109" s="2" t="n">
-        <v>0.00017202063</v>
+        <v>100915.96</v>
       </c>
       <c r="T109" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U109" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V109" s="2" t="n">
-        <v>2.822159e-05</v>
+        <v>2203.439999999988</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8730,11 +8730,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>98146.89999999999</v>
+        <v>103119.4</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>103119.4</v>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" s="2" t="n">
-        <v>91.72199999999999</v>
+        <v>54.448</v>
       </c>
       <c r="I110" s="2" t="n">
         <v>6</v>
@@ -8758,16 +8758,16 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>4972.5</v>
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>97.29244278871759</v>
+        <v>0</v>
       </c>
       <c r="N110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P110" t="b">
         <v>0</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="S110" s="2" t="n">
-        <v>98146.89999999999</v>
+        <v>103119.4</v>
       </c>
       <c r="T110" s="2" t="n">
         <v>103119.4</v>
@@ -8790,13 +8790,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V110" s="2" t="n">
-        <v>4972.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8806,11 +8806,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>4.3881446e-05</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>7.260401e-05</v>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" s="2" t="n">
-        <v>18.352</v>
+        <v>134.484</v>
       </c>
       <c r="I111" s="2" t="n">
         <v>7</v>
@@ -8834,16 +8834,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>2.8722564e-05</v>
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>39.56135878519856</v>
+        <v>0</v>
       </c>
       <c r="N111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P111" t="b">
         <v>0</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="S111" s="2" t="n">
-        <v>4.3881446</v>
+        <v>7.260401</v>
       </c>
       <c r="T111" s="2" t="n">
         <v>7.260401</v>
@@ -8866,13 +8866,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V111" s="2" t="n">
-        <v>2.872256399999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8882,11 +8882,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>98115.08</v>
+        <v>98094.44</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>98008.52</v>
@@ -8896,7 +8896,7 @@
       </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" s="2" t="n">
-        <v>52.124</v>
+        <v>55.436</v>
       </c>
       <c r="I112" s="2" t="n">
         <v>8</v>
@@ -8910,10 +8910,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>106.5599999999977</v>
+        <v>85.91999999999825</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2.084963841843242</v>
+        <v>1.681119494098833</v>
       </c>
       <c r="N112" t="b">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="S112" s="2" t="n">
-        <v>98115.08</v>
+        <v>98094.44</v>
       </c>
       <c r="T112" s="2" t="n">
         <v>98008.52</v>
@@ -8942,13 +8942,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V112" s="2" t="n">
-        <v>106.5599999999977</v>
+        <v>85.91999999999825</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8958,11 +8958,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>8.865927e-07</v>
+        <v>1.7202063e-09</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>1.4379904e-09</v>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" s="2" t="n">
-        <v>26.916</v>
+        <v>126.562</v>
       </c>
       <c r="I113" s="2" t="n">
         <v>9</v>
@@ -8986,16 +8986,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>8.851547096e-07</v>
+        <v>2.822159e-10</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1.219178171102477</v>
+        <v>0.0003887133639875507</v>
       </c>
       <c r="N113" t="b">
         <v>0</v>
       </c>
       <c r="O113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P113" t="b">
         <v>0</v>
@@ -9009,7 +9009,7 @@
         </is>
       </c>
       <c r="S113" s="2" t="n">
-        <v>0.08865927</v>
+        <v>0.00017202063</v>
       </c>
       <c r="T113" s="2" t="n">
         <v>0.00014379904</v>
@@ -9018,13 +9018,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V113" s="2" t="n">
-        <v>0.08851547096</v>
+        <v>2.822159e-05</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" s="2" t="n">
-        <v>20.184</v>
+        <v>82.965</v>
       </c>
       <c r="I114" s="2" t="n">
         <v>10</v>
@@ -9100,7 +9100,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9110,11 +9110,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>4.43071e-05</v>
+        <v>5.2289022e-05</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>7.260401e-05</v>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" s="2" t="n">
-        <v>15.43</v>
+        <v>40.705</v>
       </c>
       <c r="I115" s="2" t="n">
         <v>11</v>
@@ -9138,10 +9138,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>2.829691e-05</v>
+        <v>2.0314988e-05</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>38.97507927991641</v>
+        <v>27.98108584543508</v>
       </c>
       <c r="N115" t="b">
         <v>0</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="S115" s="2" t="n">
-        <v>4.43071</v>
+        <v>5.2289022</v>
       </c>
       <c r="T115" s="2" t="n">
         <v>7.260401</v>
@@ -9170,13 +9170,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V115" s="2" t="n">
-        <v>2.829691</v>
+        <v>2.0314988</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9186,11 +9186,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>98137.35000000001</v>
+        <v>98017.36</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>98008.52</v>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" s="2" t="n">
-        <v>12.658</v>
+        <v>35.471</v>
       </c>
       <c r="I116" s="2" t="n">
         <v>12</v>
@@ -9214,16 +9214,16 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>128.8300000000017</v>
+        <v>8.839999999996508</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2.520700936042364</v>
+        <v>0.1729643427354296</v>
       </c>
       <c r="N116" t="b">
         <v>0</v>
       </c>
       <c r="O116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P116" t="b">
         <v>0</v>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="S116" s="2" t="n">
-        <v>98137.35000000001</v>
+        <v>98017.36</v>
       </c>
       <c r="T116" s="2" t="n">
         <v>98008.52</v>
@@ -9246,13 +9246,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V116" s="2" t="n">
-        <v>128.8300000000017</v>
+        <v>8.839999999996508</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -9262,11 +9262,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.0830488e-06</v>
+        <v>1.2909707e-06</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>1.4379904e-09</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" s="2" t="n">
-        <v>14.032</v>
+        <v>113.015</v>
       </c>
       <c r="I117" s="2" t="n">
         <v>13</v>
@@ -9290,10 +9290,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>1.0816108096e-06</v>
+        <v>1.2895327096e-06</v>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1.48976927354169</v>
+        <v>1.776152929443725</v>
       </c>
       <c r="N117" t="b">
         <v>0</v>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="S117" s="2" t="n">
-        <v>0.10830488</v>
+        <v>0.12909707</v>
       </c>
       <c r="T117" s="2" t="n">
         <v>0.00014379904</v>
@@ -9322,13 +9322,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V117" s="2" t="n">
-        <v>0.10816108096</v>
+        <v>0.12895327096</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9338,11 +9338,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>103110.4</v>
+        <v>103119.4</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>103119.4</v>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" s="2" t="n">
-        <v>8.978999999999999</v>
+        <v>39.092</v>
       </c>
       <c r="I118" s="2" t="n">
         <v>14</v>
@@ -9366,13 +9366,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>0.176094919074602</v>
+        <v>0</v>
       </c>
       <c r="N118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O118" t="b">
         <v>1</v>
@@ -9389,7 +9389,7 @@
         </is>
       </c>
       <c r="S118" s="2" t="n">
-        <v>103110.4</v>
+        <v>103119.4</v>
       </c>
       <c r="T118" s="2" t="n">
         <v>103119.4</v>
@@ -9398,13 +9398,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V118" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9414,11 +9414,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>2.831073e-05</v>
+        <v>5.835816e-05</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>7.260401e-05</v>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" s="2" t="n">
-        <v>17.374</v>
+        <v>256.433</v>
       </c>
       <c r="I119" s="2" t="n">
         <v>15</v>
@@ -9442,10 +9442,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>4.429328e-05</v>
+        <v>1.424585e-05</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>61.00786621463389</v>
+        <v>19.62168778003666</v>
       </c>
       <c r="N119" t="b">
         <v>0</v>
@@ -9454,7 +9454,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q119" s="2" t="n">
         <v>100000</v>
@@ -9465,7 +9465,7 @@
         </is>
       </c>
       <c r="S119" s="2" t="n">
-        <v>2.831073</v>
+        <v>5.835815999999999</v>
       </c>
       <c r="T119" s="2" t="n">
         <v>7.260401</v>
@@ -9474,13 +9474,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V119" s="2" t="n">
-        <v>4.429328</v>
+        <v>1.424585</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9490,11 +9490,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>98190.61</v>
+        <v>98097.89999999999</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>98008.52</v>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" s="2" t="n">
-        <v>10.513</v>
+        <v>49.395</v>
       </c>
       <c r="I120" s="2" t="n">
         <v>16</v>
@@ -9518,10 +9518,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>182.0899999999965</v>
+        <v>89.3799999999901</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>3.562791534921518</v>
+        <v>1.748818207431798</v>
       </c>
       <c r="N120" t="b">
         <v>0</v>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="S120" s="2" t="n">
-        <v>98190.61</v>
+        <v>98097.89999999999</v>
       </c>
       <c r="T120" s="2" t="n">
         <v>98008.52</v>
@@ -9550,13 +9550,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V120" s="2" t="n">
-        <v>182.0899999999965</v>
+        <v>89.3799999999901</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9566,11 +9566,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>5.883410399999999e-07</v>
+        <v>1.7202063e-09</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>1.4379904e-09</v>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" s="2" t="n">
-        <v>11.729</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="I121" s="2" t="n">
         <v>17</v>
@@ -9594,10 +9594,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>5.869030495999999e-07</v>
+        <v>2.822159e-10</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>0.8083777659039347</v>
+        <v>0.0003887133639875507</v>
       </c>
       <c r="N121" t="b">
         <v>0</v>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="S121" s="2" t="n">
-        <v>0.058834104</v>
+        <v>0.00017202063</v>
       </c>
       <c r="T121" s="2" t="n">
         <v>0.00014379904</v>
@@ -9626,37 +9626,37 @@
         <v>7.26025720096</v>
       </c>
       <c r="V121" s="2" t="n">
-        <v>0.05869030495999999</v>
+        <v>2.822159e-05</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>98094.31</v>
+        <v>98146.89999999999</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
       </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" s="2" t="n">
-        <v>33.27</v>
+        <v>91.72199999999999</v>
       </c>
       <c r="I122" s="2" t="n">
         <v>6</v>
@@ -9670,10 +9670,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>85.7899999999936</v>
+        <v>4972.5</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1.67857590082322</v>
+        <v>97.29244278871759</v>
       </c>
       <c r="N122" t="b">
         <v>0</v>
@@ -9693,27 +9693,27 @@
         </is>
       </c>
       <c r="S122" s="2" t="n">
-        <v>98094.31</v>
+        <v>98146.89999999999</v>
       </c>
       <c r="T122" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="U122" s="2" t="n">
         <v>5110.87999999999</v>
       </c>
       <c r="V122" s="2" t="n">
-        <v>85.7899999999936</v>
+        <v>4972.5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9722,150 +9722,150 @@
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>103110.4</v>
+        <v>4.3881446e-05</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
       </c>
       <c r="G123" t="inlineStr"/>
       <c r="H123" s="2" t="n">
-        <v>33.024</v>
+        <v>18.352</v>
       </c>
       <c r="I123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K123" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>9</v>
+        <v>2.8722564e-05</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>0.176094919074602</v>
+        <v>39.56135878519856</v>
       </c>
       <c r="N123" t="b">
         <v>0</v>
       </c>
       <c r="O123" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P123" t="b">
         <v>0</v>
       </c>
       <c r="Q123" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S123" s="2" t="n">
-        <v>103110.4</v>
+        <v>4.3881446</v>
       </c>
       <c r="T123" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401</v>
       </c>
       <c r="U123" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V123" s="2" t="n">
-        <v>9</v>
+        <v>2.872256399999999</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>6.929935e-09</v>
+        <v>98115.08</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>98008.52</v>
       </c>
       <c r="F124" t="b">
         <v>1</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" s="2" t="n">
-        <v>35.774</v>
+        <v>52.124</v>
       </c>
       <c r="I124" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K124" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>5.491944599999999e-09</v>
+        <v>106.5599999999977</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>0.007564393998705471</v>
+        <v>2.084963841843242</v>
       </c>
       <c r="N124" t="b">
         <v>0</v>
       </c>
       <c r="O124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P124" t="b">
         <v>0</v>
       </c>
       <c r="Q124" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S124" s="2" t="n">
-        <v>0.0006929935</v>
+        <v>98115.08</v>
       </c>
       <c r="T124" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>98008.52</v>
       </c>
       <c r="U124" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V124" s="2" t="n">
-        <v>0.0005491944599999999</v>
+        <v>106.5599999999977</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9874,17 +9874,17 @@
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>3.5712448e-05</v>
+        <v>8.865927e-07</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" s="2" t="n">
-        <v>37.647</v>
+        <v>26.916</v>
       </c>
       <c r="I125" s="2" t="n">
         <v>9</v>
@@ -9898,10 +9898,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>3.6891562e-05</v>
+        <v>8.851547096e-07</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>50.81302353189629</v>
+        <v>1.219178171102477</v>
       </c>
       <c r="N125" t="b">
         <v>0</v>
@@ -9921,46 +9921,46 @@
         </is>
       </c>
       <c r="S125" s="2" t="n">
-        <v>3.5712448</v>
+        <v>0.08865927</v>
       </c>
       <c r="T125" s="2" t="n">
-        <v>7.260401</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U125" s="2" t="n">
         <v>7.26025720096</v>
       </c>
       <c r="V125" s="2" t="n">
-        <v>3.6891562</v>
+        <v>0.08851547096</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>98010.63</v>
+        <v>103110.4</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="F126" t="b">
         <v>1</v>
       </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" s="2" t="n">
-        <v>23.283</v>
+        <v>20.184</v>
       </c>
       <c r="I126" s="2" t="n">
         <v>10</v>
@@ -9974,10 +9974,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>2.110000000000582</v>
+        <v>9</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>0.04128447547194585</v>
+        <v>0.176094919074602</v>
       </c>
       <c r="N126" t="b">
         <v>0</v>
@@ -9997,198 +9997,198 @@
         </is>
       </c>
       <c r="S126" s="2" t="n">
-        <v>98010.63</v>
+        <v>103110.4</v>
       </c>
       <c r="T126" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="U126" s="2" t="n">
         <v>5110.87999999999</v>
       </c>
       <c r="V126" s="2" t="n">
-        <v>2.110000000000582</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>103100.84</v>
+        <v>4.43071e-05</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F127" t="b">
         <v>1</v>
       </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" s="2" t="n">
-        <v>16.51</v>
+        <v>15.43</v>
       </c>
       <c r="I127" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K127" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>18.55999999999767</v>
+        <v>2.829691e-05</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>0.3631468553360225</v>
+        <v>38.97507927991641</v>
       </c>
       <c r="N127" t="b">
         <v>0</v>
       </c>
       <c r="O127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P127" t="b">
         <v>0</v>
       </c>
       <c r="Q127" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S127" s="2" t="n">
-        <v>103100.84</v>
+        <v>4.43071</v>
       </c>
       <c r="T127" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401</v>
       </c>
       <c r="U127" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V127" s="2" t="n">
-        <v>18.55999999999767</v>
+        <v>2.829691</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1.6254884e-08</v>
+        <v>98137.35000000001</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>98008.52</v>
       </c>
       <c r="F128" t="b">
         <v>1</v>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" s="2" t="n">
-        <v>10.855</v>
+        <v>12.658</v>
       </c>
       <c r="I128" s="2" t="n">
         <v>12</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K128" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1.48168936e-08</v>
+        <v>128.8300000000017</v>
       </c>
       <c r="M128" s="2" t="n">
-        <v>0.020408221347917</v>
+        <v>2.520700936042364</v>
       </c>
       <c r="N128" t="b">
         <v>0</v>
       </c>
       <c r="O128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P128" t="b">
         <v>0</v>
       </c>
       <c r="Q128" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S128" s="2" t="n">
-        <v>0.0016254884</v>
+        <v>98137.35000000001</v>
       </c>
       <c r="T128" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>98008.52</v>
       </c>
       <c r="U128" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V128" s="2" t="n">
-        <v>0.00148168936</v>
+        <v>128.8300000000017</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>1.0830488e-06</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F129" t="b">
         <v>1</v>
       </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" s="2" t="n">
-        <v>38.386</v>
+        <v>14.032</v>
       </c>
       <c r="I129" s="2" t="n">
         <v>13</v>
@@ -10202,16 +10202,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>0</v>
+        <v>1.0816108096e-06</v>
       </c>
       <c r="M129" s="2" t="n">
-        <v>0</v>
+        <v>1.48976927354169</v>
       </c>
       <c r="N129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P129" t="b">
         <v>0</v>
@@ -10225,27 +10225,27 @@
         </is>
       </c>
       <c r="S129" s="2" t="n">
-        <v>7.260401</v>
+        <v>0.10830488</v>
       </c>
       <c r="T129" s="2" t="n">
-        <v>7.260401</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U129" s="2" t="n">
         <v>7.26025720096</v>
       </c>
       <c r="V129" s="2" t="n">
-        <v>0</v>
+        <v>0.10816108096</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10254,17 +10254,17 @@
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>98010.63</v>
+        <v>103110.4</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
       </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" s="2" t="n">
-        <v>26.138</v>
+        <v>8.978999999999999</v>
       </c>
       <c r="I130" s="2" t="n">
         <v>14</v>
@@ -10278,10 +10278,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>2.110000000000582</v>
+        <v>9</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>0.04128447547194585</v>
+        <v>0.176094919074602</v>
       </c>
       <c r="N130" t="b">
         <v>0</v>
@@ -10301,103 +10301,103 @@
         </is>
       </c>
       <c r="S130" s="2" t="n">
-        <v>98010.63</v>
+        <v>103110.4</v>
       </c>
       <c r="T130" s="2" t="n">
-        <v>98008.52</v>
+        <v>103119.4</v>
       </c>
       <c r="U130" s="2" t="n">
         <v>5110.87999999999</v>
       </c>
       <c r="V130" s="2" t="n">
-        <v>2.110000000000582</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>103107.33</v>
+        <v>2.831073e-05</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
       </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" s="2" t="n">
-        <v>33.057</v>
+        <v>17.374</v>
       </c>
       <c r="I131" s="2" t="n">
         <v>15</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K131" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>12.06999999999243</v>
+        <v>4.429328e-05</v>
       </c>
       <c r="M131" s="2" t="n">
-        <v>0.2361628525810126</v>
+        <v>61.00786621463389</v>
       </c>
       <c r="N131" t="b">
         <v>0</v>
       </c>
       <c r="O131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P131" t="b">
         <v>0</v>
       </c>
       <c r="Q131" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S131" s="2" t="n">
-        <v>103107.33</v>
+        <v>2.831073</v>
       </c>
       <c r="T131" s="2" t="n">
-        <v>103119.4</v>
+        <v>7.260401</v>
       </c>
       <c r="U131" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V131" s="2" t="n">
-        <v>12.06999999999243</v>
+        <v>4.429328</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10406,93 +10406,93 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>4.2327648e-07</v>
+        <v>98190.61</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>98008.52</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
       </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" s="2" t="n">
-        <v>36.948</v>
+        <v>10.513</v>
       </c>
       <c r="I132" s="2" t="n">
         <v>16</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K132" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>4.218384896e-07</v>
+        <v>182.0899999999965</v>
       </c>
       <c r="M132" s="2" t="n">
-        <v>0.5810241674967406</v>
+        <v>3.562791534921518</v>
       </c>
       <c r="N132" t="b">
         <v>0</v>
       </c>
       <c r="O132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P132" t="b">
         <v>0</v>
       </c>
       <c r="Q132" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S132" s="2" t="n">
-        <v>0.042327648</v>
+        <v>98190.61</v>
       </c>
       <c r="T132" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>98008.52</v>
       </c>
       <c r="U132" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V132" s="2" t="n">
-        <v>0.04218384896</v>
+        <v>182.0899999999965</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>6.7887515e-05</v>
+        <v>5.883410399999999e-07</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
       </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" s="2" t="n">
-        <v>27.288</v>
+        <v>11.729</v>
       </c>
       <c r="I133" s="2" t="n">
         <v>17</v>
@@ -10506,16 +10506,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>4.716495000000001e-06</v>
+        <v>5.869030495999999e-07</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>6.49631944082691</v>
+        <v>0.8083777659039347</v>
       </c>
       <c r="N133" t="b">
         <v>0</v>
       </c>
       <c r="O133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P133" t="b">
         <v>0</v>
@@ -10529,63 +10529,63 @@
         </is>
       </c>
       <c r="S133" s="2" t="n">
-        <v>6.7887515</v>
+        <v>0.058834104</v>
       </c>
       <c r="T133" s="2" t="n">
-        <v>7.260401</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U133" s="2" t="n">
         <v>7.26025720096</v>
       </c>
       <c r="V133" s="2" t="n">
-        <v>0.4716495000000001</v>
+        <v>0.05869030495999999</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>5.0181607e-05</v>
+        <v>98094.31</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F134" t="b">
         <v>1</v>
       </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" s="2" t="n">
-        <v>50.507</v>
+        <v>33.27</v>
       </c>
       <c r="I134" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K134" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>2.2422403e-05</v>
+        <v>85.7899999999936</v>
       </c>
       <c r="M134" s="2" t="n">
-        <v>30.88375849416899</v>
+        <v>1.67857590082322</v>
       </c>
       <c r="N134" t="b">
         <v>0</v>
@@ -10597,35 +10597,35 @@
         <v>0</v>
       </c>
       <c r="Q134" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S134" s="2" t="n">
-        <v>5.0181607</v>
+        <v>98094.31</v>
       </c>
       <c r="T134" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U134" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V134" s="2" t="n">
-        <v>2.2422403</v>
+        <v>85.7899999999936</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10634,34 +10634,34 @@
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>4.2327648e-07</v>
+        <v>103110.4</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F135" t="b">
         <v>1</v>
       </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" s="2" t="n">
-        <v>44.277</v>
+        <v>33.024</v>
       </c>
       <c r="I135" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K135" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>4.218384896e-07</v>
+        <v>9</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>0.5810241674967406</v>
+        <v>0.176094919074602</v>
       </c>
       <c r="N135" t="b">
         <v>0</v>
@@ -10673,71 +10673,71 @@
         <v>0</v>
       </c>
       <c r="Q135" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S135" s="2" t="n">
-        <v>0.042327648</v>
+        <v>103110.4</v>
       </c>
       <c r="T135" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U135" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V135" s="2" t="n">
-        <v>0.04218384896</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>103110.4</v>
+        <v>6.929935e-09</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F136" t="b">
         <v>1</v>
       </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" s="2" t="n">
-        <v>24.567</v>
+        <v>35.774</v>
       </c>
       <c r="I136" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K136" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>9</v>
+        <v>5.491944599999999e-09</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>0.176094919074602</v>
+        <v>0.007564393998705471</v>
       </c>
       <c r="N136" t="b">
         <v>0</v>
@@ -10749,71 +10749,71 @@
         <v>0</v>
       </c>
       <c r="Q136" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S136" s="2" t="n">
-        <v>103110.4</v>
+        <v>0.0006929935</v>
       </c>
       <c r="T136" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U136" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V136" s="2" t="n">
-        <v>9</v>
+        <v>0.0005491944599999999</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>100214.07</v>
+        <v>3.5712448e-05</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F137" t="b">
         <v>1</v>
       </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" s="2" t="n">
-        <v>48.832</v>
+        <v>37.647</v>
       </c>
       <c r="I137" s="2" t="n">
         <v>9</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K137" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>2205.550000000003</v>
+        <v>3.6891562e-05</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>43.15401652944321</v>
+        <v>50.81302353189629</v>
       </c>
       <c r="N137" t="b">
         <v>0</v>
@@ -10825,147 +10825,147 @@
         <v>0</v>
       </c>
       <c r="Q137" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S137" s="2" t="n">
-        <v>100214.07</v>
+        <v>3.5712448</v>
       </c>
       <c r="T137" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U137" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V137" s="2" t="n">
-        <v>2205.550000000003</v>
+        <v>3.6891562</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>6.925494e-05</v>
+        <v>98010.63</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F138" t="b">
         <v>1</v>
       </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" s="2" t="n">
-        <v>29.567</v>
+        <v>23.283</v>
       </c>
       <c r="I138" s="2" t="n">
         <v>10</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K138" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L138" s="2" t="n">
-        <v>3.349070000000003e-06</v>
+        <v>2.110000000000582</v>
       </c>
       <c r="M138" s="2" t="n">
-        <v>4.612880656014729</v>
+        <v>0.04128447547194585</v>
       </c>
       <c r="N138" t="b">
         <v>0</v>
       </c>
       <c r="O138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P138" t="b">
         <v>0</v>
       </c>
       <c r="Q138" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S138" s="2" t="n">
-        <v>6.925494</v>
+        <v>98010.63</v>
       </c>
       <c r="T138" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U138" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V138" s="2" t="n">
-        <v>0.3349070000000003</v>
+        <v>2.110000000000582</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>5.723616e-09</v>
+        <v>103100.84</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F139" t="b">
         <v>1</v>
       </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" s="2" t="n">
-        <v>21.08</v>
+        <v>16.51</v>
       </c>
       <c r="I139" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K139" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L139" s="2" t="n">
-        <v>4.285625599999999e-09</v>
+        <v>18.55999999999767</v>
       </c>
       <c r="M139" s="2" t="n">
-        <v>0.005902856443478786</v>
+        <v>0.3631468553360225</v>
       </c>
       <c r="N139" t="b">
         <v>0</v>
@@ -10977,35 +10977,35 @@
         <v>0</v>
       </c>
       <c r="Q139" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S139" s="2" t="n">
-        <v>0.0005723616</v>
+        <v>103100.84</v>
       </c>
       <c r="T139" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U139" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V139" s="2" t="n">
-        <v>0.0004285625599999999</v>
+        <v>18.55999999999767</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -11014,150 +11014,150 @@
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>101154.08</v>
+        <v>1.6254884e-08</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F140" t="b">
         <v>1</v>
       </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" s="2" t="n">
-        <v>125.092</v>
+        <v>10.855</v>
       </c>
       <c r="I140" s="2" t="n">
         <v>12</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K140" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1965.319999999992</v>
+        <v>1.48168936e-08</v>
       </c>
       <c r="M140" s="2" t="n">
-        <v>38.45365181729949</v>
+        <v>0.020408221347917</v>
       </c>
       <c r="N140" t="b">
         <v>0</v>
       </c>
       <c r="O140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" t="b">
         <v>0</v>
       </c>
       <c r="Q140" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S140" s="2" t="n">
-        <v>101154.08</v>
+        <v>0.0016254884</v>
       </c>
       <c r="T140" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U140" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V140" s="2" t="n">
-        <v>1965.319999999992</v>
+        <v>0.00148168936</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>103110.4</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F141" t="b">
         <v>1</v>
       </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" s="2" t="n">
-        <v>37.837</v>
+        <v>38.386</v>
       </c>
       <c r="I141" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K141" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>5101.87999999999</v>
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="n">
-        <v>99.8239050809254</v>
+        <v>0</v>
       </c>
       <c r="N141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P141" t="b">
         <v>0</v>
       </c>
       <c r="Q141" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S141" s="2" t="n">
-        <v>103110.4</v>
+        <v>7.260401</v>
       </c>
       <c r="T141" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U141" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V141" s="2" t="n">
-        <v>5101.87999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11166,110 +11166,110 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>7.0535156e-05</v>
+        <v>98010.63</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F142" t="b">
         <v>1</v>
       </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" s="2" t="n">
-        <v>21.881</v>
+        <v>26.138</v>
       </c>
       <c r="I142" s="2" t="n">
         <v>14</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K142" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>2.068853999999997e-06</v>
+        <v>2.110000000000582</v>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2.849560205286445</v>
+        <v>0.04128447547194585</v>
       </c>
       <c r="N142" t="b">
         <v>0</v>
       </c>
       <c r="O142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P142" t="b">
         <v>0</v>
       </c>
       <c r="Q142" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S142" s="2" t="n">
-        <v>7.0535156</v>
+        <v>98010.63</v>
       </c>
       <c r="T142" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U142" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V142" s="2" t="n">
-        <v>0.2068853999999997</v>
+        <v>2.110000000000582</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>8.960144e-08</v>
+        <v>103107.33</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
       </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" s="2" t="n">
-        <v>11.895</v>
+        <v>33.057</v>
       </c>
       <c r="I143" s="2" t="n">
         <v>15</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K143" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L143" s="2" t="n">
-        <v>8.81634496e-08</v>
+        <v>12.06999999999243</v>
       </c>
       <c r="M143" s="2" t="n">
-        <v>0.1214329563811354</v>
+        <v>0.2361628525810126</v>
       </c>
       <c r="N143" t="b">
         <v>0</v>
@@ -11281,111 +11281,111 @@
         <v>0</v>
       </c>
       <c r="Q143" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S143" s="2" t="n">
-        <v>0.008960144</v>
+        <v>103107.33</v>
       </c>
       <c r="T143" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U143" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V143" s="2" t="n">
-        <v>0.00881634496</v>
+        <v>12.06999999999243</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>102302.64</v>
+        <v>4.2327648e-07</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F144" t="b">
         <v>1</v>
       </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" s="2" t="n">
-        <v>75.002</v>
+        <v>36.948</v>
       </c>
       <c r="I144" s="2" t="n">
         <v>16</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K144" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>816.7599999999948</v>
+        <v>4.218384896e-07</v>
       </c>
       <c r="M144" s="2" t="n">
-        <v>15.98080956704122</v>
+        <v>0.5810241674967406</v>
       </c>
       <c r="N144" t="b">
         <v>0</v>
       </c>
       <c r="O144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P144" t="b">
         <v>0</v>
       </c>
       <c r="Q144" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S144" s="2" t="n">
-        <v>102302.64</v>
+        <v>0.042327648</v>
       </c>
       <c r="T144" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U144" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V144" s="2" t="n">
-        <v>816.7599999999948</v>
+        <v>0.04218384896</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -11394,34 +11394,34 @@
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>100922.77</v>
+        <v>6.7887515e-05</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F145" t="b">
         <v>1</v>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" s="2" t="n">
-        <v>111.37</v>
+        <v>27.288</v>
       </c>
       <c r="I145" s="2" t="n">
         <v>17</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K145" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L145" s="2" t="n">
-        <v>2914.25</v>
+        <v>4.716495000000001e-06</v>
       </c>
       <c r="M145" s="2" t="n">
-        <v>57.02051310146209</v>
+        <v>6.49631944082691</v>
       </c>
       <c r="N145" t="b">
         <v>0</v>
@@ -11433,71 +11433,71 @@
         <v>0</v>
       </c>
       <c r="Q145" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S145" s="2" t="n">
-        <v>100922.77</v>
+        <v>6.7887515</v>
       </c>
       <c r="T145" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U145" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V145" s="2" t="n">
-        <v>2914.25</v>
+        <v>0.4716495000000001</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>100849.95</v>
+        <v>5.0181607e-05</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F146" t="b">
         <v>1</v>
       </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" s="2" t="n">
-        <v>95.34699999999999</v>
+        <v>50.507</v>
       </c>
       <c r="I146" s="2" t="n">
         <v>6</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K146" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L146" s="2" t="n">
-        <v>2841.429999999993</v>
+        <v>2.2422403e-05</v>
       </c>
       <c r="M146" s="2" t="n">
-        <v>55.59570954512723</v>
+        <v>30.88375849416899</v>
       </c>
       <c r="N146" t="b">
         <v>0</v>
@@ -11509,71 +11509,71 @@
         <v>0</v>
       </c>
       <c r="Q146" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S146" s="2" t="n">
-        <v>100849.95</v>
+        <v>5.0181607</v>
       </c>
       <c r="T146" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U146" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V146" s="2" t="n">
-        <v>2841.429999999993</v>
+        <v>2.2422403</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>103107.98</v>
+        <v>4.2327648e-07</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F147" t="b">
         <v>1</v>
       </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" s="2" t="n">
-        <v>109.417</v>
+        <v>44.277</v>
       </c>
       <c r="I147" s="2" t="n">
         <v>7</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K147" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L147" s="2" t="n">
-        <v>11.41999999999825</v>
+        <v>4.218384896e-07</v>
       </c>
       <c r="M147" s="2" t="n">
-        <v>0.2234448862035164</v>
+        <v>0.5810241674967406</v>
       </c>
       <c r="N147" t="b">
         <v>0</v>
@@ -11585,35 +11585,35 @@
         <v>0</v>
       </c>
       <c r="Q147" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S147" s="2" t="n">
-        <v>103107.98</v>
+        <v>0.042327648</v>
       </c>
       <c r="T147" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U147" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V147" s="2" t="n">
-        <v>11.41999999999825</v>
+        <v>0.04218384896</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11622,110 +11622,110 @@
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>6.888981e-05</v>
+        <v>103110.4</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
       </c>
       <c r="G148" t="inlineStr"/>
       <c r="H148" s="2" t="n">
-        <v>460.744</v>
+        <v>24.567</v>
       </c>
       <c r="I148" s="2" t="n">
         <v>8</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K148" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L148" s="2" t="n">
-        <v>6.88883720096e-05</v>
+        <v>9</v>
       </c>
       <c r="M148" s="2" t="n">
-        <v>94.88420327656038</v>
+        <v>0.176094919074602</v>
       </c>
       <c r="N148" t="b">
         <v>0</v>
       </c>
       <c r="O148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q148" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S148" s="2" t="n">
-        <v>6.888981</v>
+        <v>103110.4</v>
       </c>
       <c r="T148" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U148" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V148" s="2" t="n">
-        <v>6.88883720096</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>7.0535156e-05</v>
+        <v>100214.07</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F149" t="b">
         <v>1</v>
       </c>
       <c r="G149" t="inlineStr"/>
       <c r="H149" s="2" t="n">
-        <v>81.55</v>
+        <v>48.832</v>
       </c>
       <c r="I149" s="2" t="n">
         <v>9</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K149" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L149" s="2" t="n">
-        <v>2.068853999999997e-06</v>
+        <v>2205.550000000003</v>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2.849560205286445</v>
+        <v>43.15401652944321</v>
       </c>
       <c r="N149" t="b">
         <v>0</v>
@@ -11737,35 +11737,35 @@
         <v>0</v>
       </c>
       <c r="Q149" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S149" s="2" t="n">
-        <v>7.0535156</v>
+        <v>100214.07</v>
       </c>
       <c r="T149" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U149" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V149" s="2" t="n">
-        <v>0.2068853999999997</v>
+        <v>2205.550000000003</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11774,34 +11774,34 @@
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>103083.2</v>
+        <v>6.925494e-05</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F150" t="b">
         <v>1</v>
       </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" s="2" t="n">
-        <v>142.791</v>
+        <v>29.567</v>
       </c>
       <c r="I150" s="2" t="n">
         <v>10</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K150" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L150" s="2" t="n">
-        <v>5074.679999999993</v>
+        <v>3.349070000000003e-06</v>
       </c>
       <c r="M150" s="2" t="n">
-        <v>99.29170710327777</v>
+        <v>4.612880656014729</v>
       </c>
       <c r="N150" t="b">
         <v>0</v>
@@ -11813,71 +11813,71 @@
         <v>0</v>
       </c>
       <c r="Q150" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S150" s="2" t="n">
-        <v>103083.2</v>
+        <v>6.925494</v>
       </c>
       <c r="T150" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U150" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V150" s="2" t="n">
-        <v>5074.679999999993</v>
+        <v>0.3349070000000003</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>103110.4</v>
+        <v>5.723616e-09</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
       </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" s="2" t="n">
-        <v>98.949</v>
+        <v>21.08</v>
       </c>
       <c r="I151" s="2" t="n">
         <v>11</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K151" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L151" s="2" t="n">
-        <v>9</v>
+        <v>4.285625599999999e-09</v>
       </c>
       <c r="M151" s="2" t="n">
-        <v>0.176094919074602</v>
+        <v>0.005902856443478786</v>
       </c>
       <c r="N151" t="b">
         <v>0</v>
@@ -11889,111 +11889,111 @@
         <v>0</v>
       </c>
       <c r="Q151" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S151" s="2" t="n">
-        <v>103110.4</v>
+        <v>0.0005723616</v>
       </c>
       <c r="T151" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U151" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V151" s="2" t="n">
-        <v>9</v>
+        <v>0.0004285625599999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>5.435776e-07</v>
+        <v>101154.08</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F152" t="b">
         <v>1</v>
       </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" s="2" t="n">
-        <v>158.032</v>
+        <v>125.092</v>
       </c>
       <c r="I152" s="2" t="n">
         <v>12</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K152" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L152" s="2" t="n">
-        <v>5.421396096e-07</v>
+        <v>1965.319999999992</v>
       </c>
       <c r="M152" s="2" t="n">
-        <v>0.7467223193254292</v>
+        <v>38.45365181729949</v>
       </c>
       <c r="N152" t="b">
         <v>0</v>
       </c>
       <c r="O152" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P152" t="b">
         <v>0</v>
       </c>
       <c r="Q152" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S152" s="2" t="n">
-        <v>0.05435776</v>
+        <v>101154.08</v>
       </c>
       <c r="T152" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U152" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V152" s="2" t="n">
-        <v>0.05421396096</v>
+        <v>1965.319999999992</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -12002,110 +12002,110 @@
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>103110.4</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F153" t="b">
         <v>1</v>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" s="2" t="n">
-        <v>25.653</v>
+        <v>37.837</v>
       </c>
       <c r="I153" s="2" t="n">
         <v>13</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K153" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L153" s="2" t="n">
-        <v>0</v>
+        <v>5101.87999999999</v>
       </c>
       <c r="M153" s="2" t="n">
-        <v>0</v>
+        <v>99.8239050809254</v>
       </c>
       <c r="N153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O153" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P153" t="b">
         <v>0</v>
       </c>
       <c r="Q153" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S153" s="2" t="n">
-        <v>7.260401</v>
+        <v>103110.4</v>
       </c>
       <c r="T153" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U153" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V153" s="2" t="n">
-        <v>0</v>
+        <v>5101.87999999999</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Minima</t>
+          <t>Niederschlag_Uncertainty_Maxima</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>98097.98</v>
+        <v>7.0535156e-05</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="F154" t="b">
         <v>1</v>
       </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" s="2" t="n">
-        <v>49.094</v>
+        <v>21.881</v>
       </c>
       <c r="I154" s="2" t="n">
         <v>14</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K154" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L154" s="2" t="n">
-        <v>89.45999999999185</v>
+        <v>2.068853999999997e-06</v>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1.750383495601384</v>
+        <v>2.849560205286445</v>
       </c>
       <c r="N154" t="b">
         <v>0</v>
@@ -12117,35 +12117,35 @@
         <v>0</v>
       </c>
       <c r="Q154" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S154" s="2" t="n">
-        <v>98097.98</v>
+        <v>7.0535156</v>
       </c>
       <c r="T154" s="2" t="n">
-        <v>98008.52</v>
+        <v>7.260401</v>
       </c>
       <c r="U154" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V154" s="2" t="n">
-        <v>89.45999999999185</v>
+        <v>0.2068853999999997</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Luftdruck_Value_Maxima</t>
+          <t>Niederschlag_Uncertainty_Minima</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -12154,186 +12154,186 @@
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>103003.45</v>
+        <v>8.960144e-08</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>103119.4</v>
+        <v>1.4379904e-09</v>
       </c>
       <c r="F155" t="b">
         <v>1</v>
       </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" s="2" t="n">
-        <v>42.354</v>
+        <v>11.895</v>
       </c>
       <c r="I155" s="2" t="n">
         <v>15</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Luftdruck_Value</t>
+          <t>Niederschlag_Uncertainty</t>
         </is>
       </c>
       <c r="K155" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096e-05</v>
       </c>
       <c r="L155" s="2" t="n">
-        <v>115.9499999999971</v>
+        <v>8.81634496e-08</v>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2.268689540744398</v>
+        <v>0.1214329563811354</v>
       </c>
       <c r="N155" t="b">
         <v>0</v>
       </c>
       <c r="O155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P155" t="b">
         <v>0</v>
       </c>
       <c r="Q155" s="2" t="n">
-        <v>1</v>
+        <v>100000</v>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>10⁻⁵ mm/Tag</t>
         </is>
       </c>
       <c r="S155" s="2" t="n">
-        <v>103003.45</v>
+        <v>0.008960144</v>
       </c>
       <c r="T155" s="2" t="n">
-        <v>103119.4</v>
+        <v>0.00014379904</v>
       </c>
       <c r="U155" s="2" t="n">
-        <v>5110.87999999999</v>
+        <v>7.26025720096</v>
       </c>
       <c r="V155" s="2" t="n">
-        <v>115.9499999999971</v>
+        <v>0.00881634496</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Minima</t>
+          <t>Luftdruck_Value_Maxima</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1.786659e-08</v>
+        <v>102302.64</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>1.4379904e-09</v>
+        <v>103119.4</v>
       </c>
       <c r="F156" t="b">
         <v>1</v>
       </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" s="2" t="n">
-        <v>35.685</v>
+        <v>75.002</v>
       </c>
       <c r="I156" s="2" t="n">
         <v>16</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K156" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L156" s="2" t="n">
-        <v>1.64285996e-08</v>
+        <v>816.7599999999948</v>
       </c>
       <c r="M156" s="2" t="n">
-        <v>0.02262812341941233</v>
+        <v>15.98080956704122</v>
       </c>
       <c r="N156" t="b">
         <v>0</v>
       </c>
       <c r="O156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P156" t="b">
         <v>0</v>
       </c>
       <c r="Q156" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S156" s="2" t="n">
-        <v>0.001786659</v>
+        <v>102302.64</v>
       </c>
       <c r="T156" s="2" t="n">
-        <v>0.00014379904</v>
+        <v>103119.4</v>
       </c>
       <c r="U156" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V156" s="2" t="n">
-        <v>0.00164285996</v>
+        <v>816.7599999999948</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty_Maxima</t>
+          <t>Luftdruck_Value_Minima</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>6.925494e-05</v>
+        <v>100922.77</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>7.260401e-05</v>
+        <v>98008.52</v>
       </c>
       <c r="F157" t="b">
         <v>1</v>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" s="2" t="n">
-        <v>27.166</v>
+        <v>111.37</v>
       </c>
       <c r="I157" s="2" t="n">
         <v>17</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>Niederschlag_Uncertainty</t>
+          <t>Luftdruck_Value</t>
         </is>
       </c>
       <c r="K157" s="2" t="n">
-        <v>7.26025720096e-05</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="L157" s="2" t="n">
-        <v>3.349070000000003e-06</v>
+        <v>2914.25</v>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4.612880656014729</v>
+        <v>57.02051310146209</v>
       </c>
       <c r="N157" t="b">
         <v>0</v>
@@ -12345,30 +12345,30 @@
         <v>0</v>
       </c>
       <c r="Q157" s="2" t="n">
-        <v>100000</v>
+        <v>1</v>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>10⁻⁵ mm/Tag</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="S157" s="2" t="n">
-        <v>6.925494</v>
+        <v>100922.77</v>
       </c>
       <c r="T157" s="2" t="n">
-        <v>7.260401</v>
+        <v>98008.52</v>
       </c>
       <c r="U157" s="2" t="n">
-        <v>7.26025720096</v>
+        <v>5110.87999999999</v>
       </c>
       <c r="V157" s="2" t="n">
-        <v>0.3349070000000003</v>
+        <v>2914.25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12378,11 +12378,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>98103.10000000001</v>
+        <v>100849.95</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>98008.52</v>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" s="2" t="n">
-        <v>17.722</v>
+        <v>95.34699999999999</v>
       </c>
       <c r="I158" s="2" t="n">
         <v>6</v>
@@ -12406,10 +12406,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L158" s="2" t="n">
-        <v>94.58000000000175</v>
+        <v>2841.429999999993</v>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1.850561938452907</v>
+        <v>55.59570954512723</v>
       </c>
       <c r="N158" t="b">
         <v>0</v>
@@ -12429,7 +12429,7 @@
         </is>
       </c>
       <c r="S158" s="2" t="n">
-        <v>98103.10000000001</v>
+        <v>100849.95</v>
       </c>
       <c r="T158" s="2" t="n">
         <v>98008.52</v>
@@ -12438,13 +12438,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V158" s="2" t="n">
-        <v>94.58000000000175</v>
+        <v>2841.429999999993</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -12454,11 +12454,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>103013.53</v>
+        <v>103107.98</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>103119.4</v>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="G159" t="inlineStr"/>
       <c r="H159" s="2" t="n">
-        <v>15.372</v>
+        <v>109.417</v>
       </c>
       <c r="I159" s="2" t="n">
         <v>7</v>
@@ -12482,16 +12482,16 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L159" s="2" t="n">
-        <v>105.8699999999953</v>
+        <v>11.41999999999825</v>
       </c>
       <c r="M159" s="2" t="n">
-        <v>2.07146323138081</v>
+        <v>0.2234448862035164</v>
       </c>
       <c r="N159" t="b">
         <v>0</v>
       </c>
       <c r="O159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P159" t="b">
         <v>0</v>
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="S159" s="2" t="n">
-        <v>103013.53</v>
+        <v>103107.98</v>
       </c>
       <c r="T159" s="2" t="n">
         <v>103119.4</v>
@@ -12514,13 +12514,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V159" s="2" t="n">
-        <v>105.8699999999953</v>
+        <v>11.41999999999825</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -12530,11 +12530,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1.3286352e-06</v>
+        <v>6.888981e-05</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>1.4379904e-09</v>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" s="2" t="n">
-        <v>26.358</v>
+        <v>460.744</v>
       </c>
       <c r="I160" s="2" t="n">
         <v>8</v>
@@ -12558,10 +12558,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L160" s="2" t="n">
-        <v>1.3271972096e-06</v>
+        <v>6.88883720096e-05</v>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1.828030568151923</v>
+        <v>94.88420327656038</v>
       </c>
       <c r="N160" t="b">
         <v>0</v>
@@ -12570,7 +12570,7 @@
         <v>0</v>
       </c>
       <c r="P160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q160" s="2" t="n">
         <v>100000</v>
@@ -12581,7 +12581,7 @@
         </is>
       </c>
       <c r="S160" s="2" t="n">
-        <v>0.13286352</v>
+        <v>6.888981</v>
       </c>
       <c r="T160" s="2" t="n">
         <v>0.00014379904</v>
@@ -12590,13 +12590,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V160" s="2" t="n">
-        <v>0.13271972096</v>
+        <v>6.88883720096</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -12606,11 +12606,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>5.0181607e-05</v>
+        <v>7.0535156e-05</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>7.260401e-05</v>
@@ -12620,7 +12620,7 @@
       </c>
       <c r="G161" t="inlineStr"/>
       <c r="H161" s="2" t="n">
-        <v>21.526</v>
+        <v>81.55</v>
       </c>
       <c r="I161" s="2" t="n">
         <v>9</v>
@@ -12634,10 +12634,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L161" s="2" t="n">
-        <v>2.2422403e-05</v>
+        <v>2.068853999999997e-06</v>
       </c>
       <c r="M161" s="2" t="n">
-        <v>30.88375849416899</v>
+        <v>2.849560205286445</v>
       </c>
       <c r="N161" t="b">
         <v>0</v>
@@ -12657,7 +12657,7 @@
         </is>
       </c>
       <c r="S161" s="2" t="n">
-        <v>5.0181607</v>
+        <v>7.0535156</v>
       </c>
       <c r="T161" s="2" t="n">
         <v>7.260401</v>
@@ -12666,13 +12666,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V161" s="2" t="n">
-        <v>2.2422403</v>
+        <v>0.2068853999999997</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -12682,11 +12682,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>101197.62</v>
+        <v>103083.2</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>98008.52</v>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" s="2" t="n">
-        <v>15.442</v>
+        <v>142.791</v>
       </c>
       <c r="I162" s="2" t="n">
         <v>10</v>
@@ -12710,10 +12710,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L162" s="2" t="n">
-        <v>3189.099999999991</v>
+        <v>5074.679999999993</v>
       </c>
       <c r="M162" s="2" t="n">
-        <v>62.39825626897907</v>
+        <v>99.29170710327777</v>
       </c>
       <c r="N162" t="b">
         <v>0</v>
@@ -12733,7 +12733,7 @@
         </is>
       </c>
       <c r="S162" s="2" t="n">
-        <v>101197.62</v>
+        <v>103083.2</v>
       </c>
       <c r="T162" s="2" t="n">
         <v>98008.52</v>
@@ -12742,13 +12742,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V162" s="2" t="n">
-        <v>3189.099999999991</v>
+        <v>5074.679999999993</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12758,11 +12758,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>100417.94</v>
+        <v>103110.4</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>103119.4</v>
@@ -12772,7 +12772,7 @@
       </c>
       <c r="G163" t="inlineStr"/>
       <c r="H163" s="2" t="n">
-        <v>32.175</v>
+        <v>98.949</v>
       </c>
       <c r="I163" s="2" t="n">
         <v>11</v>
@@ -12786,16 +12786,16 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L163" s="2" t="n">
-        <v>2701.459999999992</v>
+        <v>9</v>
       </c>
       <c r="M163" s="2" t="n">
-        <v>52.85704223147476</v>
+        <v>0.176094919074602</v>
       </c>
       <c r="N163" t="b">
         <v>0</v>
       </c>
       <c r="O163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P163" t="b">
         <v>0</v>
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="S163" s="2" t="n">
-        <v>100417.94</v>
+        <v>103110.4</v>
       </c>
       <c r="T163" s="2" t="n">
         <v>103119.4</v>
@@ -12818,13 +12818,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V163" s="2" t="n">
-        <v>2701.459999999992</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12834,11 +12834,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>9.930495000000001e-07</v>
+        <v>5.435776e-07</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>1.4379904e-09</v>
@@ -12848,7 +12848,7 @@
       </c>
       <c r="G164" t="inlineStr"/>
       <c r="H164" s="2" t="n">
-        <v>12.123</v>
+        <v>158.032</v>
       </c>
       <c r="I164" s="2" t="n">
         <v>12</v>
@@ -12862,16 +12862,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L164" s="2" t="n">
-        <v>9.916115096000001e-07</v>
+        <v>5.421396096e-07</v>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1.365807687183427</v>
+        <v>0.7467223193254292</v>
       </c>
       <c r="N164" t="b">
         <v>0</v>
       </c>
       <c r="O164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P164" t="b">
         <v>0</v>
@@ -12885,7 +12885,7 @@
         </is>
       </c>
       <c r="S164" s="2" t="n">
-        <v>0.09930495</v>
+        <v>0.05435776</v>
       </c>
       <c r="T164" s="2" t="n">
         <v>0.00014379904</v>
@@ -12894,13 +12894,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V164" s="2" t="n">
-        <v>0.09916115096000001</v>
+        <v>0.05421396096</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12910,11 +12910,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>5.22469e-05</v>
+        <v>7.260401e-05</v>
       </c>
       <c r="E165" s="2" t="n">
         <v>7.260401e-05</v>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" s="2" t="n">
-        <v>41.596</v>
+        <v>25.653</v>
       </c>
       <c r="I165" s="2" t="n">
         <v>13</v>
@@ -12938,16 +12938,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L165" s="2" t="n">
-        <v>2.035711e-05</v>
+        <v>0</v>
       </c>
       <c r="M165" s="2" t="n">
-        <v>28.03910307379777</v>
+        <v>0</v>
       </c>
       <c r="N165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P165" t="b">
         <v>0</v>
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="S165" s="2" t="n">
-        <v>5.224690000000001</v>
+        <v>7.260401</v>
       </c>
       <c r="T165" s="2" t="n">
         <v>7.260401</v>
@@ -12970,13 +12970,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V165" s="2" t="n">
-        <v>2.035711</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12986,11 +12986,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>98192.60000000001</v>
+        <v>98097.98</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>98008.52</v>
@@ -13000,7 +13000,7 @@
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" s="2" t="n">
-        <v>15.017</v>
+        <v>49.094</v>
       </c>
       <c r="I166" s="2" t="n">
         <v>14</v>
@@ -13014,10 +13014,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L166" s="2" t="n">
-        <v>184.0800000000017</v>
+        <v>89.45999999999185</v>
       </c>
       <c r="M166" s="2" t="n">
-        <v>3.601728078139227</v>
+        <v>1.750383495601384</v>
       </c>
       <c r="N166" t="b">
         <v>0</v>
@@ -13037,7 +13037,7 @@
         </is>
       </c>
       <c r="S166" s="2" t="n">
-        <v>98192.60000000001</v>
+        <v>98097.98</v>
       </c>
       <c r="T166" s="2" t="n">
         <v>98008.52</v>
@@ -13046,13 +13046,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V166" s="2" t="n">
-        <v>184.0800000000017</v>
+        <v>89.45999999999185</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13062,11 +13062,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>IsoGlyph</t>
+          <t>VSUP</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>101803.04</v>
+        <v>103003.45</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>103119.4</v>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="G167" t="inlineStr"/>
       <c r="H167" s="2" t="n">
-        <v>19.371</v>
+        <v>42.354</v>
       </c>
       <c r="I167" s="2" t="n">
         <v>15</v>
@@ -13090,10 +13090,10 @@
         <v>5110.87999999999</v>
       </c>
       <c r="L167" s="2" t="n">
-        <v>1316.360000000001</v>
+        <v>115.9499999999971</v>
       </c>
       <c r="M167" s="2" t="n">
-        <v>25.75603418589369</v>
+        <v>2.268689540744398</v>
       </c>
       <c r="N167" t="b">
         <v>0</v>
@@ -13113,7 +13113,7 @@
         </is>
       </c>
       <c r="S167" s="2" t="n">
-        <v>101803.04</v>
+        <v>103003.45</v>
       </c>
       <c r="T167" s="2" t="n">
         <v>103119.4</v>
@@ -13122,13 +13122,13 @@
         <v>5110.87999999999</v>
       </c>
       <c r="V167" s="2" t="n">
-        <v>1316.360000000001</v>
+        <v>115.9499999999971</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -13138,11 +13138,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>ScaledGlyph</t>
+          <t>IsoGlyph</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>9.97824e-07</v>
+        <v>1.786659e-08</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>1.4379904e-09</v>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="G168" t="inlineStr"/>
       <c r="H168" s="2" t="n">
-        <v>16.2</v>
+        <v>35.685</v>
       </c>
       <c r="I168" s="2" t="n">
         <v>16</v>
@@ -13166,16 +13166,16 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L168" s="2" t="n">
-        <v>9.963860096000001e-07</v>
+        <v>1.64285996e-08</v>
       </c>
       <c r="M168" s="2" t="n">
-        <v>1.372383900488059</v>
+        <v>0.02262812341941233</v>
       </c>
       <c r="N168" t="b">
         <v>0</v>
       </c>
       <c r="O168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P168" t="b">
         <v>0</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="S168" s="2" t="n">
-        <v>0.09978240000000001</v>
+        <v>0.001786659</v>
       </c>
       <c r="T168" s="2" t="n">
         <v>0.00014379904</v>
@@ -13198,13 +13198,13 @@
         <v>7.26025720096</v>
       </c>
       <c r="V168" s="2" t="n">
-        <v>0.09963860096</v>
+        <v>0.00164285996</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -13214,11 +13214,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>VSUP</t>
+          <t>ScaledGlyph</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>4.243185e-05</v>
+        <v>6.925494e-05</v>
       </c>
       <c r="E169" s="2" t="n">
         <v>7.260401e-05</v>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="G169" t="inlineStr"/>
       <c r="H169" s="2" t="n">
-        <v>16.087</v>
+        <v>27.166</v>
       </c>
       <c r="I169" s="2" t="n">
         <v>17</v>
@@ -13242,10 +13242,10 @@
         <v>7.26025720096e-05</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>3.017216e-05</v>
+        <v>3.349070000000003e-06</v>
       </c>
       <c r="M169" s="2" t="n">
-        <v>41.55797675598935</v>
+        <v>4.612880656014729</v>
       </c>
       <c r="N169" t="b">
         <v>0</v>
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="S169" s="2" t="n">
-        <v>4.243185</v>
+        <v>6.925494</v>
       </c>
       <c r="T169" s="2" t="n">
         <v>7.260401</v>
@@ -13274,11 +13274,923 @@
         <v>7.26025720096</v>
       </c>
       <c r="V169" s="2" t="n">
+        <v>0.3349070000000003</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>98103.10000000001</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F170" t="b">
+        <v>1</v>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" s="2" t="n">
+        <v>17.722</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>94.58000000000175</v>
+      </c>
+      <c r="M170" s="2" t="n">
+        <v>1.850561938452907</v>
+      </c>
+      <c r="N170" t="b">
+        <v>0</v>
+      </c>
+      <c r="O170" t="b">
+        <v>0</v>
+      </c>
+      <c r="P170" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q170" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="S170" s="2" t="n">
+        <v>98103.10000000001</v>
+      </c>
+      <c r="T170" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="U170" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>94.58000000000175</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>103013.53</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F171" t="b">
+        <v>1</v>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" s="2" t="n">
+        <v>15.372</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>105.8699999999953</v>
+      </c>
+      <c r="M171" s="2" t="n">
+        <v>2.07146323138081</v>
+      </c>
+      <c r="N171" t="b">
+        <v>0</v>
+      </c>
+      <c r="O171" t="b">
+        <v>0</v>
+      </c>
+      <c r="P171" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="S171" s="2" t="n">
+        <v>103013.53</v>
+      </c>
+      <c r="T171" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="U171" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="V171" s="2" t="n">
+        <v>105.8699999999953</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>1.3286352e-06</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F172" t="b">
+        <v>1</v>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" s="2" t="n">
+        <v>26.358</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>1.3271972096e-06</v>
+      </c>
+      <c r="M172" s="2" t="n">
+        <v>1.828030568151923</v>
+      </c>
+      <c r="N172" t="b">
+        <v>0</v>
+      </c>
+      <c r="O172" t="b">
+        <v>0</v>
+      </c>
+      <c r="P172" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q172" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="S172" s="2" t="n">
+        <v>0.13286352</v>
+      </c>
+      <c r="T172" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="U172" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="V172" s="2" t="n">
+        <v>0.13271972096</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>5.0181607e-05</v>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F173" t="b">
+        <v>1</v>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" s="2" t="n">
+        <v>21.526</v>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>2.2422403e-05</v>
+      </c>
+      <c r="M173" s="2" t="n">
+        <v>30.88375849416899</v>
+      </c>
+      <c r="N173" t="b">
+        <v>0</v>
+      </c>
+      <c r="O173" t="b">
+        <v>0</v>
+      </c>
+      <c r="P173" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="S173" s="2" t="n">
+        <v>5.0181607</v>
+      </c>
+      <c r="T173" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="U173" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="V173" s="2" t="n">
+        <v>2.2422403</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>101197.62</v>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F174" t="b">
+        <v>1</v>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" s="2" t="n">
+        <v>15.442</v>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>3189.099999999991</v>
+      </c>
+      <c r="M174" s="2" t="n">
+        <v>62.39825626897907</v>
+      </c>
+      <c r="N174" t="b">
+        <v>0</v>
+      </c>
+      <c r="O174" t="b">
+        <v>0</v>
+      </c>
+      <c r="P174" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="S174" s="2" t="n">
+        <v>101197.62</v>
+      </c>
+      <c r="T174" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="U174" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="V174" s="2" t="n">
+        <v>3189.099999999991</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>100417.94</v>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F175" t="b">
+        <v>1</v>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" s="2" t="n">
+        <v>32.175</v>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>2701.459999999992</v>
+      </c>
+      <c r="M175" s="2" t="n">
+        <v>52.85704223147476</v>
+      </c>
+      <c r="N175" t="b">
+        <v>0</v>
+      </c>
+      <c r="O175" t="b">
+        <v>0</v>
+      </c>
+      <c r="P175" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="S175" s="2" t="n">
+        <v>100417.94</v>
+      </c>
+      <c r="T175" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="U175" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="V175" s="2" t="n">
+        <v>2701.459999999992</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>9.930495000000001e-07</v>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F176" t="b">
+        <v>1</v>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" s="2" t="n">
+        <v>12.123</v>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>9.916115096000001e-07</v>
+      </c>
+      <c r="M176" s="2" t="n">
+        <v>1.365807687183427</v>
+      </c>
+      <c r="N176" t="b">
+        <v>0</v>
+      </c>
+      <c r="O176" t="b">
+        <v>0</v>
+      </c>
+      <c r="P176" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="n">
+        <v>0.09930495</v>
+      </c>
+      <c r="T176" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="U176" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="V176" s="2" t="n">
+        <v>0.09916115096000001</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>5.22469e-05</v>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F177" t="b">
+        <v>1</v>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" s="2" t="n">
+        <v>41.596</v>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>2.035711e-05</v>
+      </c>
+      <c r="M177" s="2" t="n">
+        <v>28.03910307379777</v>
+      </c>
+      <c r="N177" t="b">
+        <v>0</v>
+      </c>
+      <c r="O177" t="b">
+        <v>0</v>
+      </c>
+      <c r="P177" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="S177" s="2" t="n">
+        <v>5.224690000000001</v>
+      </c>
+      <c r="T177" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="U177" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="V177" s="2" t="n">
+        <v>2.035711</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>98192.60000000001</v>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F178" t="b">
+        <v>1</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" s="2" t="n">
+        <v>15.017</v>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>184.0800000000017</v>
+      </c>
+      <c r="M178" s="2" t="n">
+        <v>3.601728078139227</v>
+      </c>
+      <c r="N178" t="b">
+        <v>0</v>
+      </c>
+      <c r="O178" t="b">
+        <v>0</v>
+      </c>
+      <c r="P178" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="S178" s="2" t="n">
+        <v>98192.60000000001</v>
+      </c>
+      <c r="T178" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="U178" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="V178" s="2" t="n">
+        <v>184.0800000000017</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>101803.04</v>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F179" t="b">
+        <v>1</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" s="2" t="n">
+        <v>19.371</v>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>1316.360000000001</v>
+      </c>
+      <c r="M179" s="2" t="n">
+        <v>25.75603418589369</v>
+      </c>
+      <c r="N179" t="b">
+        <v>0</v>
+      </c>
+      <c r="O179" t="b">
+        <v>0</v>
+      </c>
+      <c r="P179" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="n">
+        <v>101803.04</v>
+      </c>
+      <c r="T179" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="U179" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="V179" s="2" t="n">
+        <v>1316.360000000001</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>9.97824e-07</v>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F180" t="b">
+        <v>1</v>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" s="2" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>9.963860096000001e-07</v>
+      </c>
+      <c r="M180" s="2" t="n">
+        <v>1.372383900488059</v>
+      </c>
+      <c r="N180" t="b">
+        <v>0</v>
+      </c>
+      <c r="O180" t="b">
+        <v>0</v>
+      </c>
+      <c r="P180" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="n">
+        <v>0.09978240000000001</v>
+      </c>
+      <c r="T180" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="U180" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="V180" s="2" t="n">
+        <v>0.09963860096</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>4.243185e-05</v>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F181" t="b">
+        <v>1</v>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" s="2" t="n">
+        <v>16.087</v>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>3.017216e-05</v>
+      </c>
+      <c r="M181" s="2" t="n">
+        <v>41.55797675598935</v>
+      </c>
+      <c r="N181" t="b">
+        <v>0</v>
+      </c>
+      <c r="O181" t="b">
+        <v>0</v>
+      </c>
+      <c r="P181" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="S181" s="2" t="n">
+        <v>4.243185</v>
+      </c>
+      <c r="T181" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="U181" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="V181" s="2" t="n">
         <v>3.017216</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V169"/>
+  <autoFilter ref="A1:V181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Nutzerstudie/Assets/Results/Analysis_Output/Identifikation/00_Identifikation_Einzelantworten.xlsx
+++ b/Nutzerstudie/Assets/Results/Analysis_Output/Identifikation/00_Identifikation_Einzelantworten.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Einzelantworten" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einzelantworten'!$A$1:$W$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Einzelantworten'!$A$1:$W$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W181"/>
+  <dimension ref="A1:W205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -5472,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" s="2" t="n">
         <v>100000</v>
@@ -14004,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="Q172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" s="2" t="n">
         <v>100000</v>
@@ -14738,8 +14738,1904 @@
         <v>3.017216</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G182" t="b">
+        <v>1</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" s="2" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M182" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="N182" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="O182" t="b">
+        <v>0</v>
+      </c>
+      <c r="P182" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="b">
+        <v>0</v>
+      </c>
+      <c r="R182" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="U182" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="V182" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W182" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>103107.33</v>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G183" t="b">
+        <v>1</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" s="2" t="n">
+        <v>33.756</v>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M183" s="2" t="n">
+        <v>12.06999999999243</v>
+      </c>
+      <c r="N183" s="2" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="O183" t="b">
+        <v>0</v>
+      </c>
+      <c r="P183" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q183" t="b">
+        <v>0</v>
+      </c>
+      <c r="R183" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="n">
+        <v>103107.33</v>
+      </c>
+      <c r="U183" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="V183" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W183" s="2" t="n">
+        <v>12.06999999999243</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>8.079795e-07</v>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" t="b">
+        <v>1</v>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" s="2" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L184" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M184" s="2" t="n">
+        <v>8.065415096e-07</v>
+      </c>
+      <c r="N184" s="2" t="n">
+        <v>1.11089936248175</v>
+      </c>
+      <c r="O184" t="b">
+        <v>0</v>
+      </c>
+      <c r="P184" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="b">
+        <v>0</v>
+      </c>
+      <c r="R184" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="n">
+        <v>0.08079794999999999</v>
+      </c>
+      <c r="U184" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="V184" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W184" s="2" t="n">
+        <v>0.08065415095999999</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G185" t="b">
+        <v>1</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" s="2" t="n">
+        <v>16.111</v>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L185" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="b">
+        <v>1</v>
+      </c>
+      <c r="P185" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q185" t="b">
+        <v>0</v>
+      </c>
+      <c r="R185" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="U185" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="V185" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W185" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>98021.57000000001</v>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G186" t="b">
+        <v>1</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" s="2" t="n">
+        <v>17.778</v>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L186" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M186" s="2" t="n">
+        <v>13.05000000000291</v>
+      </c>
+      <c r="N186" s="2" t="n">
+        <v>0.2553376326582298</v>
+      </c>
+      <c r="O186" t="b">
+        <v>0</v>
+      </c>
+      <c r="P186" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q186" t="b">
+        <v>0</v>
+      </c>
+      <c r="R186" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="n">
+        <v>98021.57000000001</v>
+      </c>
+      <c r="U186" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="V186" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W186" s="2" t="n">
+        <v>13.05000000000291</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>103107.33</v>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G187" t="b">
+        <v>1</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" s="2" t="n">
+        <v>10.465</v>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L187" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M187" s="2" t="n">
+        <v>12.06999999999243</v>
+      </c>
+      <c r="N187" s="2" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="O187" t="b">
+        <v>0</v>
+      </c>
+      <c r="P187" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q187" t="b">
+        <v>0</v>
+      </c>
+      <c r="R187" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="n">
+        <v>103107.33</v>
+      </c>
+      <c r="U187" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="V187" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W187" s="2" t="n">
+        <v>12.06999999999243</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="n">
+        <v>3.1291847e-08</v>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G188" t="b">
+        <v>1</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" s="2" t="n">
+        <v>24.021</v>
+      </c>
+      <c r="J188" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L188" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M188" s="2" t="n">
+        <v>2.98538566e-08</v>
+      </c>
+      <c r="N188" s="2" t="n">
+        <v>0.0411195578526509</v>
+      </c>
+      <c r="O188" t="b">
+        <v>0</v>
+      </c>
+      <c r="P188" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q188" t="b">
+        <v>0</v>
+      </c>
+      <c r="R188" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T188" s="2" t="n">
+        <v>0.0031291847</v>
+      </c>
+      <c r="U188" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="V188" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W188" s="2" t="n">
+        <v>0.00298538566</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="n">
+        <v>7.0535156e-05</v>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G189" t="b">
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" s="2" t="n">
+        <v>46.473</v>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L189" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M189" s="2" t="n">
+        <v>2.068853999999997e-06</v>
+      </c>
+      <c r="N189" s="2" t="n">
+        <v>2.849560205286445</v>
+      </c>
+      <c r="O189" t="b">
+        <v>0</v>
+      </c>
+      <c r="P189" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="b">
+        <v>0</v>
+      </c>
+      <c r="R189" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T189" s="2" t="n">
+        <v>7.0535156</v>
+      </c>
+      <c r="U189" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="V189" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W189" s="2" t="n">
+        <v>0.2068853999999997</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="n">
+        <v>98021.57000000001</v>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G190" t="b">
+        <v>1</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" s="2" t="n">
+        <v>11.893</v>
+      </c>
+      <c r="J190" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L190" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M190" s="2" t="n">
+        <v>13.05000000000291</v>
+      </c>
+      <c r="N190" s="2" t="n">
+        <v>0.2553376326582298</v>
+      </c>
+      <c r="O190" t="b">
+        <v>0</v>
+      </c>
+      <c r="P190" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q190" t="b">
+        <v>0</v>
+      </c>
+      <c r="R190" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="n">
+        <v>98021.57000000001</v>
+      </c>
+      <c r="U190" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="V190" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W190" s="2" t="n">
+        <v>13.05000000000291</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="n">
+        <v>103083.2</v>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G191" t="b">
+        <v>1</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" s="2" t="n">
+        <v>8.162000000000001</v>
+      </c>
+      <c r="J191" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L191" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M191" s="2" t="n">
+        <v>36.19999999999709</v>
+      </c>
+      <c r="N191" s="2" t="n">
+        <v>0.7082928967222309</v>
+      </c>
+      <c r="O191" t="b">
+        <v>0</v>
+      </c>
+      <c r="P191" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q191" t="b">
+        <v>0</v>
+      </c>
+      <c r="R191" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="n">
+        <v>103083.2</v>
+      </c>
+      <c r="U191" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="V191" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W191" s="2" t="n">
+        <v>36.19999999999709</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="n">
+        <v>2.6435309e-08</v>
+      </c>
+      <c r="E192" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G192" t="b">
+        <v>1</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" s="2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J192" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L192" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M192" s="2" t="n">
+        <v>2.49973186e-08</v>
+      </c>
+      <c r="N192" s="2" t="n">
+        <v>0.03443034855114319</v>
+      </c>
+      <c r="O192" t="b">
+        <v>0</v>
+      </c>
+      <c r="P192" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q192" t="b">
+        <v>0</v>
+      </c>
+      <c r="R192" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T192" s="2" t="n">
+        <v>0.0026435309</v>
+      </c>
+      <c r="U192" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="V192" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W192" s="2" t="n">
+        <v>0.00249973186</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="n">
+        <v>5.2339587e-05</v>
+      </c>
+      <c r="E193" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G193" t="b">
+        <v>1</v>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" s="2" t="n">
+        <v>10.467</v>
+      </c>
+      <c r="J193" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L193" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M193" s="2" t="n">
+        <v>2.0264423e-05</v>
+      </c>
+      <c r="N193" s="2" t="n">
+        <v>27.91143955247274</v>
+      </c>
+      <c r="O193" t="b">
+        <v>0</v>
+      </c>
+      <c r="P193" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="b">
+        <v>0</v>
+      </c>
+      <c r="R193" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T193" s="2" t="n">
+        <v>5.2339587</v>
+      </c>
+      <c r="U193" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="V193" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W193" s="2" t="n">
+        <v>2.0264423</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="n">
+        <v>6.821413e-09</v>
+      </c>
+      <c r="E194" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G194" t="b">
+        <v>1</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" s="2" t="n">
+        <v>87.48</v>
+      </c>
+      <c r="J194" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L194" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M194" s="2" t="n">
+        <v>5.3834226e-09</v>
+      </c>
+      <c r="N194" s="2" t="n">
+        <v>0.007414919955298784</v>
+      </c>
+      <c r="O194" t="b">
+        <v>0</v>
+      </c>
+      <c r="P194" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q194" t="b">
+        <v>0</v>
+      </c>
+      <c r="R194" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="n">
+        <v>0.0006821412999999999</v>
+      </c>
+      <c r="U194" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="V194" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W194" s="2" t="n">
+        <v>0.00053834226</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="n">
+        <v>98181.17</v>
+      </c>
+      <c r="E195" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G195" t="b">
+        <v>1</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" s="2" t="n">
+        <v>354.47</v>
+      </c>
+      <c r="J195" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L195" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M195" s="2" t="n">
+        <v>172.6499999999942</v>
+      </c>
+      <c r="N195" s="2" t="n">
+        <v>3.378087530914334</v>
+      </c>
+      <c r="O195" t="b">
+        <v>0</v>
+      </c>
+      <c r="P195" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="b">
+        <v>0</v>
+      </c>
+      <c r="R195" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T195" s="2" t="n">
+        <v>98181.17</v>
+      </c>
+      <c r="U195" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="V195" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W195" s="2" t="n">
+        <v>172.6499999999942</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G196" t="b">
+        <v>1</v>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" s="2" t="n">
+        <v>467.251</v>
+      </c>
+      <c r="J196" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L196" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="b">
+        <v>1</v>
+      </c>
+      <c r="P196" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q196" t="b">
+        <v>0</v>
+      </c>
+      <c r="R196" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="U196" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="V196" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W196" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="n">
+        <v>103083.2</v>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G197" t="b">
+        <v>1</v>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" s="2" t="n">
+        <v>82.38200000000001</v>
+      </c>
+      <c r="J197" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L197" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M197" s="2" t="n">
+        <v>36.19999999999709</v>
+      </c>
+      <c r="N197" s="2" t="n">
+        <v>0.7082928967222309</v>
+      </c>
+      <c r="O197" t="b">
+        <v>0</v>
+      </c>
+      <c r="P197" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q197" t="b">
+        <v>0</v>
+      </c>
+      <c r="R197" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T197" s="2" t="n">
+        <v>103083.2</v>
+      </c>
+      <c r="U197" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="V197" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W197" s="2" t="n">
+        <v>36.19999999999709</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="n">
+        <v>3.0688227e-07</v>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G198" t="b">
+        <v>1</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" s="2" t="n">
+        <v>84.735</v>
+      </c>
+      <c r="J198" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L198" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M198" s="2" t="n">
+        <v>3.054442796e-07</v>
+      </c>
+      <c r="N198" s="2" t="n">
+        <v>0.42070724375937</v>
+      </c>
+      <c r="O198" t="b">
+        <v>0</v>
+      </c>
+      <c r="P198" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q198" t="b">
+        <v>0</v>
+      </c>
+      <c r="R198" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T198" s="2" t="n">
+        <v>0.030688227</v>
+      </c>
+      <c r="U198" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="V198" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W198" s="2" t="n">
+        <v>0.03054442796</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="n">
+        <v>98021.57000000001</v>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G199" t="b">
+        <v>1</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" s="2" t="n">
+        <v>163.835</v>
+      </c>
+      <c r="J199" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L199" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M199" s="2" t="n">
+        <v>13.05000000000291</v>
+      </c>
+      <c r="N199" s="2" t="n">
+        <v>0.2553376326582298</v>
+      </c>
+      <c r="O199" t="b">
+        <v>0</v>
+      </c>
+      <c r="P199" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q199" t="b">
+        <v>0</v>
+      </c>
+      <c r="R199" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T199" s="2" t="n">
+        <v>98021.57000000001</v>
+      </c>
+      <c r="U199" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="V199" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W199" s="2" t="n">
+        <v>13.05000000000291</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="n">
+        <v>7.0535156e-05</v>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G200" t="b">
+        <v>1</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" s="2" t="n">
+        <v>115.839</v>
+      </c>
+      <c r="J200" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L200" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M200" s="2" t="n">
+        <v>2.068853999999997e-06</v>
+      </c>
+      <c r="N200" s="2" t="n">
+        <v>2.849560205286445</v>
+      </c>
+      <c r="O200" t="b">
+        <v>0</v>
+      </c>
+      <c r="P200" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q200" t="b">
+        <v>0</v>
+      </c>
+      <c r="R200" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="n">
+        <v>7.0535156</v>
+      </c>
+      <c r="U200" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="V200" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W200" s="2" t="n">
+        <v>0.2068853999999997</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="n">
+        <v>103107.33</v>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G201" t="b">
+        <v>1</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" s="2" t="n">
+        <v>62.584</v>
+      </c>
+      <c r="J201" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L201" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M201" s="2" t="n">
+        <v>12.06999999999243</v>
+      </c>
+      <c r="N201" s="2" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="O201" t="b">
+        <v>0</v>
+      </c>
+      <c r="P201" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q201" t="b">
+        <v>0</v>
+      </c>
+      <c r="R201" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="n">
+        <v>103107.33</v>
+      </c>
+      <c r="U201" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="V201" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W201" s="2" t="n">
+        <v>12.06999999999243</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="n">
+        <v>2.09749e-06</v>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>1.4379904e-09</v>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G202" t="b">
+        <v>1</v>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" s="2" t="n">
+        <v>105.498</v>
+      </c>
+      <c r="J202" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L202" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M202" s="2" t="n">
+        <v>2.0960520096e-06</v>
+      </c>
+      <c r="N202" s="2" t="n">
+        <v>2.887021701273676</v>
+      </c>
+      <c r="O202" t="b">
+        <v>0</v>
+      </c>
+      <c r="P202" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q202" t="b">
+        <v>0</v>
+      </c>
+      <c r="R202" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="n">
+        <v>0.209749</v>
+      </c>
+      <c r="U202" s="2" t="n">
+        <v>0.00014379904</v>
+      </c>
+      <c r="V202" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W202" s="2" t="n">
+        <v>0.20960520096</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="n">
+        <v>98010.63</v>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G203" t="b">
+        <v>1</v>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" s="2" t="n">
+        <v>37.417</v>
+      </c>
+      <c r="J203" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L203" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M203" s="2" t="n">
+        <v>2.110000000000582</v>
+      </c>
+      <c r="N203" s="2" t="n">
+        <v>0.04128447547194585</v>
+      </c>
+      <c r="O203" t="b">
+        <v>0</v>
+      </c>
+      <c r="P203" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q203" t="b">
+        <v>0</v>
+      </c>
+      <c r="R203" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T203" s="2" t="n">
+        <v>98010.63</v>
+      </c>
+      <c r="U203" s="2" t="n">
+        <v>98008.52</v>
+      </c>
+      <c r="V203" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W203" s="2" t="n">
+        <v>2.110000000000582</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>7.260401e-05</v>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G204" t="b">
+        <v>1</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" s="2" t="n">
+        <v>66.206</v>
+      </c>
+      <c r="J204" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty</t>
+        </is>
+      </c>
+      <c r="L204" s="2" t="n">
+        <v>7.26025720096e-05</v>
+      </c>
+      <c r="M204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" t="b">
+        <v>1</v>
+      </c>
+      <c r="P204" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q204" t="b">
+        <v>0</v>
+      </c>
+      <c r="R204" s="2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>10⁻⁵ mm/Tag</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="U204" s="2" t="n">
+        <v>7.260401</v>
+      </c>
+      <c r="V204" s="2" t="n">
+        <v>7.26025720096</v>
+      </c>
+      <c r="W204" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="n">
+        <v>103083.2</v>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G205" t="b">
+        <v>1</v>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" s="2" t="n">
+        <v>115.361</v>
+      </c>
+      <c r="J205" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value</t>
+        </is>
+      </c>
+      <c r="L205" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="M205" s="2" t="n">
+        <v>36.19999999999709</v>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>0.7082928967222309</v>
+      </c>
+      <c r="O205" t="b">
+        <v>0</v>
+      </c>
+      <c r="P205" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q205" t="b">
+        <v>0</v>
+      </c>
+      <c r="R205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="n">
+        <v>103083.2</v>
+      </c>
+      <c r="U205" s="2" t="n">
+        <v>103119.4</v>
+      </c>
+      <c r="V205" s="2" t="n">
+        <v>5110.87999999999</v>
+      </c>
+      <c r="W205" s="2" t="n">
+        <v>36.19999999999709</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W181"/>
+  <autoFilter ref="A1:W205"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>